--- a/News GIS.xlsx
+++ b/News GIS.xlsx
@@ -1,25 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haide\Desktop\Work\hazmat-gis\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18200" windowHeight="8510"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Data"/>
+    <sheet name="Data" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlcn.WorksheetConnection_DataB1B71">Data!$B$1:$B$7</definedName>
     <definedName name="_xlcn.WorksheetConnection_DataD1D71">Data!$D$1:$D$7</definedName>
     <definedName name="_xlcn.WorksheetConnection_DataE1E71">Data!$E$1:$E$7</definedName>
   </definedNames>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="87">
   <si>
     <t>Type</t>
   </si>
@@ -117,13 +122,13 @@
     <t>Radiological</t>
   </si>
   <si>
-    <t xml:space="preserve">Radiation Leak Detected at Metallurgical Plant in Eastern France </t>
+    <t>Radiation Leak Detected at Metallurgical Plant in Eastern France </t>
   </si>
   <si>
     <t>France</t>
   </si>
   <si>
-    <t xml:space="preserve">Colmar </t>
+    <t>Colmar </t>
   </si>
   <si>
     <t>https://sputnikglobe.com/20240411/radiation-leak-detected-at-metallurgical-plant-in-eastern-france---reports-1117875818.html</t>
@@ -138,7 +143,7 @@
     <t>Canada</t>
   </si>
   <si>
-    <t xml:space="preserve">Burlington </t>
+    <t>Burlington </t>
   </si>
   <si>
     <t>https://www.insauga.com/worker-dies-after-chemical-exposure-at-burlington-warehouse/</t>
@@ -252,7 +257,7 @@
     <t>Bulgaria</t>
   </si>
   <si>
-    <t xml:space="preserve">Kozloduy </t>
+    <t>Kozloduy </t>
   </si>
   <si>
     <t>Economic</t>
@@ -267,7 +272,7 @@
     <t>China</t>
   </si>
   <si>
-    <t xml:space="preserve">Ningxia </t>
+    <t>Ningxia </t>
   </si>
   <si>
     <t>https://www.powderbulksolids.com/industrial-fires-explosions/2-killed-in-chemical-plant-explosion</t>
@@ -280,17 +285,13 @@
   </si>
   <si>
     <t>https://abc11.com/gas-leak-30-000-pound-propane-tank/14689532/</t>
-  </si>
-  <si>
-    <t>Sacramento</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -340,43 +341,42 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -387,10 +387,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -428,71 +428,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -520,7 +520,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -543,11 +543,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -556,13 +556,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -572,7 +572,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -581,7 +581,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -590,7 +590,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -598,10 +598,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -671,22 +671,21 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" style="7" width="7.433571428571429" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="10.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="83.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="20.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="12.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="10.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="9" width="8.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="9" width="8.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="11.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="7" width="7.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="7" width="111.14785714285713" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="7.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.54296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="83.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.81640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="8.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.81640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.54296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="111.1796875" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:11" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -721,7 +720,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" spans="1:11" ht="18.75" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
@@ -756,7 +755,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row r="3" spans="1:11" ht="18.75" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
@@ -791,7 +790,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row r="4" spans="1:11" ht="18.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
@@ -826,7 +825,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row r="5" spans="1:11" ht="18.75" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -861,7 +860,7 @@
         <v>35</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+    <row r="6" spans="1:11" ht="19.5" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>11</v>
       </c>
@@ -896,7 +895,7 @@
         <v>40</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+    <row r="7" spans="1:11" ht="19.5" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
@@ -931,7 +930,7 @@
         <v>44</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+    <row r="8" spans="1:11" ht="19.5" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>45</v>
       </c>
@@ -966,7 +965,7 @@
         <v>48</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+    <row r="9" spans="1:11" ht="19.5" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -1001,7 +1000,7 @@
         <v>51</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+    <row r="10" spans="1:11" ht="19.5" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
@@ -1036,7 +1035,7 @@
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+    <row r="11" spans="1:11" ht="19.5" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
@@ -1071,7 +1070,7 @@
         <v>59</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+    <row r="12" spans="1:11" ht="19.5" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>45</v>
       </c>
@@ -1106,7 +1105,7 @@
         <v>63</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+    <row r="13" spans="1:11" ht="19.5" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>11</v>
       </c>
@@ -1141,7 +1140,7 @@
         <v>67</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+    <row r="14" spans="1:11" ht="19.5" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
@@ -1176,7 +1175,7 @@
         <v>70</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
+    <row r="15" spans="1:11" ht="19.5" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>11</v>
       </c>
@@ -1211,7 +1210,7 @@
         <v>74</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
+    <row r="16" spans="1:11" ht="19.5" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>45</v>
       </c>
@@ -1246,7 +1245,7 @@
         <v>79</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
+    <row r="17" spans="1:11" ht="19.5" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>11</v>
       </c>
@@ -1281,7 +1280,7 @@
         <v>83</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+    <row r="18" spans="1:11" ht="19.5" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>11</v>
       </c>
@@ -1316,40 +1315,18 @@
         <v>86</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
-      <c r="A19" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F19" s="5">
-        <v>45320</v>
-      </c>
-      <c r="G19" s="6">
-        <v>0</v>
-      </c>
-      <c r="H19" s="6">
-        <v>0</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>18</v>
-      </c>
+    <row r="19" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/News GIS.xlsx
+++ b/News GIS.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K215"/>
+  <dimension ref="A1:K228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1527,12 +1527,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Algeria, China</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Algiers, China</t>
+          <t>Algiers</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -1573,21 +1573,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IAEA Chief holds high level talks in Belarus</t>
+          <t>Algeria and China Discuss Expanding Cooperation in Nuclear Technologies</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Minsk</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>45572</v>
+        <v>45566</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://www.neimagazine.com/news/iaea-chief-holds-high-level-talks-in-belarus/</t>
+          <t>https://al24news.com/en/algeria-and-china-discuss-expanding-cooperation-in-nuclear-technologies/</t>
         </is>
       </c>
     </row>
@@ -1624,21 +1624,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rooppur NPP Engineers Receive Training in Nuclear Fuel Handling</t>
+          <t>IAEA Chief holds high level talks in Belarus</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Belarus</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Minsk</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45566</v>
+        <v>45572</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://energycentral.com/news/rooppur-npp-engineers-receive-training-nuclear-fuel-handling</t>
+          <t>https://www.neimagazine.com/news/iaea-chief-holds-high-level-talks-in-belarus/</t>
         </is>
       </c>
     </row>
@@ -1675,17 +1675,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Report Explores Use Cases for Advanced Nuclear Energy</t>
+          <t>Rooppur NPP Engineers Receive Training in Nuclear Fuel Handling</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://www.power-eng.com/nuclear/smrs/report-explores-use-cases-for-advanced-nuclear-energy/#gref</t>
+          <t>https://energycentral.com/news/rooppur-npp-engineers-receive-training-nuclear-fuel-handling</t>
         </is>
       </c>
     </row>
@@ -1726,17 +1726,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Politecnico di Milano Designated as IAEA Collaborating Centre</t>
+          <t>Report Explores Use Cases for Advanced Nuclear Energy</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Washington DC</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/news/politecnico-di-milano-designated-as-iaea-collaborating-centre</t>
+          <t>https://www.power-eng.com/nuclear/smrs/report-explores-use-cases-for-advanced-nuclear-energy/#gref</t>
         </is>
       </c>
     </row>
@@ -1777,15 +1777,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Independent Review Assesses IAEA's Internal Safety Regulatory System</t>
+          <t>Politecnico di Milano Designated as IAEA Collaborating Centre</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Milan</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="n">
         <v>45566</v>
       </c>
@@ -1807,7 +1811,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/pressreleases/independent-review-assesses-iaeas-internal-safety-regulatory-system-for-first-time-finds-well-established-framework</t>
+          <t>https://www.iaea.org/newscenter/news/politecnico-di-milano-designated-as-iaea-collaborating-centre</t>
         </is>
       </c>
     </row>
@@ -2023,22 +2027,26 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>COVID May Increase Risk of Death Years After Infection</t>
+          <t>IAEA Director General Statement on Situation in Ukraine</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Kyiv</t>
+        </is>
+      </c>
       <c r="F32" s="2" t="n">
-        <v>45574</v>
+        <v>45566</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -2058,34 +2066,34 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://www.allsides.com/news/2024-10-09-1415/coronavirus-covid-may-increase-risk-death-years-after-infection-study</t>
+          <t>https://www.iaea.org/newscenter/pressreleases/update-254-iaea-director-general-statement-on-situation-in-ukraine</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IAEA Director General Statement on Situation in Ukraine</t>
+          <t>China Tightens Rules on Hazardous Cargo at Ningbo Port</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Ningbo</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -2099,7 +2107,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2109,7 +2117,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/pressreleases/update-254-iaea-director-general-statement-on-situation-in-ukraine</t>
+          <t>https://theloadstar.com/china-tightens-rules-on-hazardous-cargo-at-ningbo/</t>
         </is>
       </c>
     </row>
@@ -2126,17 +2134,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>China Tightens Rules on Hazardous Cargo at Ningbo Port</t>
+          <t>Execution to Start for Major Egypt Chemicals Project</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ningbo</t>
+          <t>Cairo</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
@@ -2150,7 +2158,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2160,7 +2168,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://theloadstar.com/china-tightens-rules-on-hazardous-cargo-at-ningbo/</t>
+          <t>https://www.meed.com/execution-to-start-for-major-egypt-chemicals-project</t>
         </is>
       </c>
     </row>
@@ -2172,22 +2180,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Execution to Start for Major Egypt Chemicals Project</t>
+          <t>IAEA Concludes Long Term Operation Safety Review at Sweden's Oskarshamn Nuclear Power Plant</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cairo</t>
+          <t>Oskarshamn</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
@@ -2201,7 +2209,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2211,32 +2219,36 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://www.meed.com/execution-to-start-for-major-egypt-chemicals-project</t>
+          <t>https://www.iaea.org/newscenter/pressreleases/iaea-concludes-long-term-operation-safety-review-at-swedens-oskarshamn-nuclear-power-plant</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>7th International Conference on CBRNE Research and Innovation, 2026</t>
+          <t>Ukraine to Consider New Nuclear Safety Measures Amidst Conflict</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Kyiv</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="n">
         <v>45566</v>
       </c>
@@ -2258,7 +2270,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://ctif.org/events/7th-international-conference-cbrne-research-and-innovation-2026</t>
+          <t>https://www.pravda.com.ua/eng/news/2024/10/10/7479090/</t>
         </is>
       </c>
     </row>
@@ -2275,15 +2287,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Voters Back Nuclear Power Plant Construction in National Referendum</t>
+          <t>Korea, Czech Republic Team Up on Hydrogen Production Using Nuclear Power</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
+          <t>Korea</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Seoul</t>
+        </is>
+      </c>
       <c r="F37" s="2" t="n">
         <v>45566</v>
       </c>
@@ -2305,32 +2321,36 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://www.nucnet.org/news/voters-back-nuclear-power-plant-construction-in-national-referendum-10-1-2024</t>
+          <t>https://www.world-nuclear-news.org/articles/korea-czech-republic-team-up-on-hydrogen-production</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Industry Lays Groundwork for Reactor Deployment with First Comprehensive Set of Rules</t>
+          <t>Iran backed Houthis Attack Chemical Tanker in Red Sea, No Injuries or Fire Reported</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>Yemen</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Sanaa</t>
+        </is>
+      </c>
       <c r="F38" s="2" t="n">
         <v>45566</v>
       </c>
@@ -2352,34 +2372,34 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://www.nucnet.org/news/industry-lays-groundwork-for-reactor-deployment-with-first-comprehensive-set-of-rules-10-1-2024</t>
+          <t>https://www.timesofisrael.com/iran-backed-houthis-attack-chemical-tanker-in-red-sea-no-injuries-or-fire-reported/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IAEA Concludes Long Term Operation Safety Review at Sweden's Oskarshamn Nuclear Power Plant</t>
+          <t>Iran backed Houthis Attack Chemical Tanker in Red Sea, No Injuries or Fire Reported</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oskarshamn</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
@@ -2393,7 +2413,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2403,7 +2423,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/pressreleases/iaea-concludes-long-term-operation-safety-review-at-swedens-oskarshamn-nuclear-power-plant</t>
+          <t>https://www.timesofisrael.com/iran-backed-houthis-attack-chemical-tanker-in-red-sea-no-injuries-or-fire-reported/</t>
         </is>
       </c>
     </row>
@@ -2420,17 +2440,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ukraine to Consider New Nuclear Safety Measures Amidst Conflict</t>
+          <t>Iran Threatens to Escalate If Israel Attacks, Says Nuclear or Oil Targets a Red Line</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -2454,7 +2474,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://www.pravda.com.ua/eng/news/2024/10/10/7479090/</t>
+          <t>https://www.timesofisrael.com/iran-threatens-to-escalate-if-israel-attacks-says-nuclear-or-oil-targets-a-red-line/</t>
         </is>
       </c>
     </row>
@@ -2471,17 +2491,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Korea, Czech Republic Team Up on Hydrogen Production Using Nuclear Power</t>
+          <t>China Boron 10 Enrichment Could Revolutionize Nuclear Energy</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Seoul</t>
+          <t>Beijing</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
@@ -2505,7 +2525,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://www.world-nuclear-news.org/articles/korea-czech-republic-team-up-on-hydrogen-production</t>
+          <t>https://interestingengineering.com/energy/china-boron-10-enrichment-nuclear-energy</t>
         </is>
       </c>
     </row>
@@ -2517,26 +2537,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Iran backed Houthis Attack Chemical Tanker in Red Sea, No Injuries or Fire Reported</t>
+          <t>Iran Hit by Heavy Cyberattacks Targeting Its nuclear Facilities Amid Middle East Tensions</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Yemen, Iran</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sanaa, Tehran</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>45566</v>
+        <v>45577</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -2546,7 +2566,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2556,14 +2576,14 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://www.timesofisrael.com/iran-backed-houthis-attack-chemical-tanker-in-red-sea-no-injuries-or-fire-reported/</t>
+          <t>https://www.news18.com/world/iran-hit-by-heavy-cyberattacks-targeting-its-nuclear-facilities-amid-middle-east-tensions-9083699.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2573,17 +2593,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Iran Threatens to Escalate If Israel Attacks, Says Nuclear or Oil Targets a Red Line</t>
+          <t>Slovakia Gets USD5 Million Grant for SMR Project</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Bratislava</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
@@ -2597,7 +2617,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2607,7 +2627,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://www.timesofisrael.com/iran-threatens-to-escalate-if-israel-attacks-says-nuclear-or-oil-targets-a-red-line/</t>
+          <t>https://www.world-nuclear-news.org/articles/Slovakia%20gets%20USD5%20million%20grant%20for%20SMR%20project</t>
         </is>
       </c>
     </row>
@@ -2624,17 +2644,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>China Boron 10 Enrichment Could Revolutionize Nuclear Energy</t>
+          <t>First Reactor Launched for Yakutia nuclear Icebreaker</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Yakutia</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
@@ -2648,7 +2668,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2658,14 +2678,14 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://interestingengineering.com/energy/china-boron-10-enrichment-nuclear-energy</t>
+          <t>https://www.world-nuclear-news.org/articles/First%20reactor%20launched%20for%20Yakutia%20nuclear%20icebreaker</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2675,21 +2695,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Iran Hit by Heavy Cyberattacks Targeting Its nuclear Facilities Amid Middle East Tensions</t>
+          <t>Digital Twin of APR1400 Control Systems Created</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Seoul</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>45577</v>
+        <v>45566</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -2709,7 +2729,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://www.news18.com/world/iran-hit-by-heavy-cyberattacks-targeting-its-nuclear-facilities-amid-middle-east-tensions-9083699.html</t>
+          <t>https://www.world-nuclear-news.org/articles/digital-twin-of-apr1400-control-systems-created</t>
         </is>
       </c>
     </row>
@@ -2726,17 +2746,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Slovakia Gets USD5 Million Grant for SMR Project</t>
+          <t>Nuclear Power Generator for Deep Space Missions Unveiled</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bratislava</t>
+          <t>Washington DC</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
@@ -2750,7 +2770,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2760,7 +2780,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://www.world-nuclear-news.org/articles/Slovakia%20gets%20USD5%20million%20grant%20for%20SMR%20project</t>
+          <t>https://interestingengineering.com/energy/nuclear-power-generator-for-deep-space-missions</t>
         </is>
       </c>
     </row>
@@ -2777,15 +2797,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NucNet Launches Global Small Modular and Advanced Reactor Database</t>
+          <t>US Startup Aims for Shipyard SMR Construction</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Washington DC</t>
+        </is>
+      </c>
       <c r="F47" s="2" t="n">
         <v>45566</v>
       </c>
@@ -2807,7 +2831,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://www.nucnet.org/news/nucnet-launches-global-small-modular-and-advanced-reactor-database-10-4-2024</t>
+          <t>https://www.world-nuclear-news.org/articles/us-startup-aims-for-shipyard-smr-construction</t>
         </is>
       </c>
     </row>
@@ -2819,20 +2843,24 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plasma Heating Prediction Made 10 Million Times Faster in Fusion Research</t>
+          <t>NIST Chem Bio AI Models</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Washington DC</t>
+        </is>
+      </c>
       <c r="F48" s="2" t="n">
         <v>45566</v>
       </c>
@@ -2844,7 +2872,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2854,34 +2882,34 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://interestingengineering.com/Economic/plasma-heating-prediction-made-10-million-times-faster</t>
+          <t>https://fedscoop.com/nist-chem-bio-ai-models/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>First Reactor Launched for Yakutia nuclear Icebreaker</t>
+          <t>Abu Dhabi Gears to Host WHO Emergency Medical Teams</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Yakutia</t>
+          <t>Abu Dhabi</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
@@ -2895,7 +2923,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2905,34 +2933,34 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://www.world-nuclear-news.org/articles/First%20reactor%20launched%20for%20Yakutia%20nuclear%20icebreaker</t>
+          <t>https://www.wam.ae/en/article/b5n9q21-abu-dhabi-gears-host-who-emergency-medical-teams</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Digital Twin of APR1400 Control Systems Created</t>
+          <t>Chemical Leak Triggers Emergency in Texas</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Seoul</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
@@ -2946,7 +2974,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2956,24 +2984,24 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://www.world-nuclear-news.org/articles/digital-twin-of-apr1400-control-systems-created</t>
+          <t>https://www.bignewsnetwork.com/news/274695158/chemical-leak-triggers-emergency-in-texas</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Nuclear Power Generator for Deep Space Missions Unveiled</t>
+          <t>2 New Monkeypox Cases Identified in Hawaii</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2983,11 +3011,11 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>Hawaii</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>45566</v>
+        <v>45576</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -3007,7 +3035,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://interestingengineering.com/energy/nuclear-power-generator-for-deep-space-missions</t>
+          <t>https://bigislandnow.com/2024/10/11/2-new-monkeypox-cases-idd-in-hawaii/</t>
         </is>
       </c>
     </row>
@@ -3019,26 +3047,26 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US Startup Aims for Shipyard SMR Construction</t>
+          <t>Second Round of Polio Vaccination in Gaza Aims to Vaccinate Over Half a Million Children</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Palestine</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>Gaza</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>45566</v>
+        <v>45576</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -3048,7 +3076,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3058,7 +3086,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://www.world-nuclear-news.org/articles/us-startup-aims-for-shipyard-smr-construction</t>
+          <t>https://www.who.int/news/item/11-10-2024-second-round-of-polio-vaccination-in-the-gaza-strip-aims-to-vaccinate-over-half-a-million-children</t>
         </is>
       </c>
     </row>
@@ -3070,22 +3098,26 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Radiological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>The Role of IAEA in Nuclear and Radiological Emergency Response</t>
+          <t>Government Panel Rules on Rehabilitation of Ranger Uranium Mine</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Canberra</t>
+        </is>
+      </c>
       <c r="F53" s="2" t="n">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -3095,7 +3127,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Environmental</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3105,7 +3137,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/news/from-preparedness-to-resilience-the-role-of-the-iaea-in-nuclear-and-radiological-emergency-response</t>
+          <t>https://www.nucnet.org/news/gov-t-panel-rules-on-rehabilitation-of-ranger-uranium-mine-10-3-2024</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3149,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NIST Chem Bio AI Models</t>
+          <t>US Firm Develops nuclear Fusion Device Prototype</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3146,7 +3178,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3156,38 +3188,38 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://fedscoop.com/nist-chem-bio-ai-models/</t>
+          <t>https://interestingengineering.com/Economic/us-firm-nuclear-fusion-device-prototype</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Abu Dhabi Gears to Host WHO Emergency Medical Teams</t>
+          <t>Marburg Virus Disease: What You Need to Know</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>London</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>45566</v>
+        <v>45573</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -3207,34 +3239,34 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://www.wam.ae/en/article/b5n9q21-abu-dhabi-gears-host-who-emergency-medical-teams</t>
+          <t>https://ukhsa.blog.gov.uk/2024/10/08/marburg-virus-disease-what-you-need-to-know/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chemical Leak Triggers Emergency in Texas</t>
+          <t>Australia is already a successful nuclear nation</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Canberra</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
@@ -3248,7 +3280,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3258,7 +3290,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/274695158/chemical-leak-triggers-emergency-in-texas</t>
+          <t>https://www.spectator.com.au/2024/10/australia-is-already-a-successful-nuclear-nation/</t>
         </is>
       </c>
     </row>
@@ -3270,26 +3302,26 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2 New Monkeypox Cases Identified in Hawaii</t>
+          <t>Iranian Earthquake Sparks Debate Over Potential nuclear Testing</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hawaii</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45576</v>
+        <v>45566</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -3299,7 +3331,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3309,7 +3341,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://bigislandnow.com/2024/10/11/2-new-monkeypox-cases-idd-in-hawaii/</t>
+          <t>https://www.msn.com/en-us/news/world/iranian-earthquake-sparks-debate-over-potential-nuclear-testing/ar-AA1sbEQI</t>
         </is>
       </c>
     </row>
@@ -3321,26 +3353,26 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Explosive</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Second Round of Polio Vaccination in Gaza Aims to Vaccinate Over Half a Million Children</t>
+          <t>Azerbaijan’s Liberated Territories Have Nearly 1 Million Hectares of Hazardous Areas</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Palestine</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Gaza</t>
+          <t>Baku</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45576</v>
+        <v>45566</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -3350,7 +3382,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Environmental</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3360,7 +3392,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://www.who.int/news/item/11-10-2024-second-round-of-polio-vaccination-in-the-gaza-strip-aims-to-vaccinate-over-half-a-million-children</t>
+          <t>https://en.apa.az/social/azerbaijans-liberated-territories-has-nearly-1-million-167-thousand-hectares-of-hazardous-areas-anama-451169</t>
         </is>
       </c>
     </row>
@@ -3377,21 +3409,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Government Panel Rules on Rehabilitation of Ranger Uranium Mine</t>
+          <t>First SMR Projects Selected by European Industrial Alliance</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Canberra</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>45568</v>
+        <v>45579</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -3401,7 +3433,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3411,7 +3443,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://www.nucnet.org/news/gov-t-panel-rules-on-rehabilitation-of-ranger-uranium-mine-10-3-2024</t>
+          <t>https://www.world-nuclear-news.org/articles/first-smr-projects-selected-by-european-industrial-alliance</t>
         </is>
       </c>
     </row>
@@ -3428,21 +3460,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US Firm Develops nuclear Fusion Device Prototype</t>
+          <t>First SMR Projects Selected by European Industrial Alliance</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45566</v>
+        <v>45579</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -3452,7 +3484,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3462,7 +3494,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://interestingengineering.com/Economic/us-firm-nuclear-fusion-device-prototype</t>
+          <t>https://www.world-nuclear-news.org/articles/first-smr-projects-selected-by-european-industrial-alliance</t>
         </is>
       </c>
     </row>
@@ -3474,22 +3506,26 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AI Discovers Over 160,000 New RNA Viruses</t>
+          <t>First SMR Projects Selected by European Industrial Alliance</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Moscow</t>
+        </is>
+      </c>
       <c r="F61" s="2" t="n">
-        <v>45566</v>
+        <v>45579</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -3499,7 +3535,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3509,38 +3545,38 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://scitechdaily.com/revolutionizing-virology-ai-discovers-over-160000-new-rna-viruses/</t>
+          <t>https://www.world-nuclear-news.org/articles/first-smr-projects-selected-by-european-industrial-alliance</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Marburg Virus Disease: What You Need to Know</t>
+          <t>Iran nuclear Cyberattack Targets</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>45573</v>
+        <v>45579</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -3550,7 +3586,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3560,7 +3596,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://ukhsa.blog.gov.uk/2024/10/08/marburg-virus-disease-what-you-need-to-know/</t>
+          <t>https://www.iranintl.com/en/202410142621</t>
         </is>
       </c>
     </row>
@@ -3572,22 +3608,26 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Study Finds Evidence of Chemical Leak at Major Facility</t>
+          <t>Westinghouse Signs MOU with Shipbuilder for Nuclear New Build</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Washington DC</t>
+        </is>
+      </c>
       <c r="F63" s="2" t="n">
-        <v>45581</v>
+        <v>45566</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -3597,7 +3637,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3607,7 +3647,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://redirect.viglink.com?u=https%3A%2F%2Fwww.nature.com%2Farticles%2Fs41467-024-53085-9&amp;key=a7e37b5f6ff1de9cb410158b1013e54a&amp;prodOvrd=RAC&amp;opt=false</t>
+          <t>https://www.nucnet.org/news/westinghouse-signs-nuclear-new-build-mou-with-shipbuilder-seaspan-10-1-2024</t>
         </is>
       </c>
     </row>
@@ -3624,17 +3664,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Australia is already a successful nuclear nation</t>
+          <t>Israel’s Infrastructure Stance Amid Regional Tensions</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Canberra</t>
+          <t>Tel Aviv</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
@@ -3648,7 +3688,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3658,7 +3698,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://www.spectator.com.au/2024/10/australia-is-already-a-successful-nuclear-nation/</t>
+          <t>https://www.jpost.com/breaking-news/article-824605</t>
         </is>
       </c>
     </row>
@@ -3670,22 +3710,26 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Uranium Enrichment Milestones: Urenco Centrifuge Developments</t>
+          <t>Marburg Disease Quarantine Strengthened in Vietnam</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Hanoi</t>
+        </is>
+      </c>
       <c r="F65" s="2" t="n">
-        <v>45566</v>
+        <v>45581</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -3695,7 +3739,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3705,34 +3749,34 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://interestingengineering.com/Economic/uranium-enrichment-urenco-centrifuge-milestones</t>
+          <t>https://en.sggp.org.vn/health-sector-strengthens-strict-quarantine-measures-to-prevent-marburg-disease-post113100.html</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Radiological</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Iranian Earthquake Sparks Debate Over Potential nuclear Testing</t>
+          <t>IAEA to Begin Additional Measures at Fukushima Daiichi Nuclear Plant</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Fukushima</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
@@ -3746,7 +3790,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3756,38 +3800,38 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-us/news/world/iranian-earthquake-sparks-debate-over-potential-nuclear-testing/ar-AA1sbEQI</t>
+          <t>https://www.iaea.org/newscenter/pressreleases/iaea-initiates-first-practical-steps-of-additional-measures-at-sea-near-fukushima-daiichi-nuclear-power-station</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Azerbaijan’s Liberated Territories Have Nearly 1 Million Hectares of Hazardous Areas</t>
+          <t>Khamenei Orders Acceleration of Iran’s Infrastructure Weapons Program</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Baku</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>45566</v>
+        <v>45580</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -3797,7 +3841,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3807,7 +3851,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://en.apa.az/social/azerbaijans-liberated-territories-has-nearly-1-million-167-thousand-hectares-of-hazardous-areas-anama-451169</t>
+          <t>https://www.ncr-iran.org/en/ncri-statements/statement-nuclear/khamenei-orders-acceleration-of-nuclear-weapon-production-to-ensure-iranian-regimes-survival/</t>
         </is>
       </c>
     </row>
@@ -3824,17 +3868,21 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>WHO Warns of Rising Pandemic Threats</t>
+          <t>CDC &amp; Clemson Develop Disease Software for Flu Outbreaks</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Clemson</t>
+        </is>
+      </c>
       <c r="F68" s="2" t="n">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -3854,38 +3902,38 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://www.wam.ae/en/article/b5ogl9j-new-risks-raise-pandemic-threat-global-scale-who</t>
+          <t>https://www.postandcourier.com/greenville/clemson-news/cdc-clemson-disease-software-flu-outbreaks/article_a6584d48-865d-11ef-a1e7-330ecfad26b5.html</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>First SMR Projects Selected by European Industrial Alliance</t>
+          <t>Afghanistan Reports Infectious Disease Outbreaks</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Germany, France, Russia</t>
+          <t>Afghanistan</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Berlin, Paris, Moscow</t>
+          <t>Kabul</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>45579</v>
+        <v>45594</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -3895,7 +3943,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3905,38 +3953,38 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://www.world-nuclear-news.org/articles/first-smr-projects-selected-by-european-industrial-alliance</t>
+          <t>https://reliefweb.int/report/afghanistan/afghanistan-infectious-disease-outbreaks-epidemiological-week-40-29-sep-05-oct-2024-situation-report-40</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Iran nuclear Cyberattack Targets</t>
+          <t>Seychelles Sets Up New Chemical, Biological, Radiological, and Nuclear Team</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>45579</v>
+        <v>45581</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -3946,7 +3994,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -3956,24 +4004,24 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://www.iranintl.com/en/202410142621</t>
+          <t>http://www.seychellesnewsagency.com/articles/21384/Seychelles+sets+up+new+chemical%2C+biological%2C+radiological+and+nuclear+team</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Explosive</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Westinghouse Signs MOU with Shipbuilder for Nuclear New Build</t>
+          <t>Columbia Heights Building Fined for Hazardous Conditions After Gas Explosion</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3983,11 +4031,11 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>Columbia</t>
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>45566</v>
+        <v>45580</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -4007,7 +4055,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://www.nucnet.org/news/westinghouse-signs-nuclear-new-build-mou-with-shipbuilder-seaspan-10-1-2024</t>
+          <t>https://thewash.org/2024/10/15/columbia-heights-building-owners-fined-for-hazardous-unsafe-conditions-after-gas-explosion/</t>
         </is>
       </c>
     </row>
@@ -4024,21 +4072,21 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Israel’s Infrastructure Stance Amid Regional Tensions</t>
+          <t>BRICS members set to increase nuclear energy cooperation</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Tel Aviv</t>
+          <t>Brasilia</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>45566</v>
+        <v>45392</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -4048,7 +4096,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4058,7 +4106,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://www.jpost.com/breaking-news/article-824605</t>
+          <t>https://www.world-nuclear-news.org/articles/brics-members-set-to-increase-nuclear-energy-cooperation</t>
         </is>
       </c>
     </row>
@@ -4070,26 +4118,26 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Marburg Disease Quarantine Strengthened in Vietnam</t>
+          <t>BRICS members set to increase nuclear energy cooperation</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hanoi</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45581</v>
+        <v>45392</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -4099,7 +4147,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4109,7 +4157,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://en.sggp.org.vn/health-sector-strengthens-strict-quarantine-measures-to-prevent-marburg-disease-post113100.html</t>
+          <t>https://www.world-nuclear-news.org/articles/brics-members-set-to-increase-nuclear-energy-cooperation</t>
         </is>
       </c>
     </row>
@@ -4121,22 +4169,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Radiological</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>IAEA to Begin Additional Measures at Fukushima Daiichi Nuclear Plant</t>
+          <t>US Army Pilots Fly for Lifesaving Chemical Surety Program</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Fukushima</t>
+          <t>Washington DC</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
@@ -4160,7 +4208,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/pressreleases/iaea-initiates-first-practical-steps-of-additional-measures-at-sea-near-fukushima-daiichi-nuclear-power-station</t>
+          <t>https://www.army.mil/article/280511/seasoned_us_army_civilian_pilots_fly_missions_for_lifesaving_chemical_surety_program</t>
         </is>
       </c>
     </row>
@@ -4172,26 +4220,26 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Khamenei Orders Acceleration of Iran’s Infrastructure Weapons Program</t>
+          <t>Hazardous Material Leak at Water Treatment Plant in Lebanon County</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Lebanon County</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>45580</v>
+        <v>45568</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -4201,7 +4249,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4211,7 +4259,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://www.ncr-iran.org/en/ncri-statements/statement-nuclear/khamenei-orders-acceleration-of-nuclear-weapon-production-to-ensure-iranian-regimes-survival/</t>
+          <t>https://local21news.com/news/local/fire-crews-on-scene-of-hazardous-material-leak-at-water-treatment-plant-in-lebanon-county</t>
         </is>
       </c>
     </row>
@@ -4223,12 +4271,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CDC &amp; Clemson Develop Disease Software for Flu Outbreaks</t>
+          <t>DOE Signs Off on Oklo Fuel Fabrication Facility Design</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4238,11 +4286,11 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Clemson</t>
+          <t>Washington DC</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>45568</v>
+        <v>45566</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -4252,7 +4300,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4262,38 +4310,38 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://www.postandcourier.com/greenville/clemson-news/cdc-clemson-disease-software-flu-outbreaks/article_a6584d48-865d-11ef-a1e7-330ecfad26b5.html</t>
+          <t>https://www.world-nuclear-news.org/articles/doe-signs-off-on-oklo-fuel-fabrication-facility-design</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Afghanistan Reports Infectious Disease Outbreaks</t>
+          <t>Restart Continues with Shimane 2, Due Back Online in December</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Afghanistan</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kabul</t>
+          <t>Shimane</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>45594</v>
+        <v>45568</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -4303,7 +4351,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4313,7 +4361,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://reliefweb.int/report/afghanistan/afghanistan-infectious-disease-outbreaks-epidemiological-week-40-29-sep-05-oct-2024-situation-report-40</t>
+          <t>https://www.nucnet.org/news/restarts-continue-with-shimane-2-due-back-online-in-december-10-3-2024</t>
         </is>
       </c>
     </row>
@@ -4325,20 +4373,24 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Radiological</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Google Signs Deal to Buy Power from SMRs for Data Centres</t>
+          <t>Chinese State Owned Nuclear Company Claims Breakthrough in Radiation Detection Chip</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
       <c r="F78" s="2" t="n">
         <v>45566</v>
       </c>
@@ -4360,14 +4412,14 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://www.nucnet.org/news/google-signs-world-first-deal-to-buy-power-from-small-modular-reactors-for-data-centres-10-2-2024</t>
+          <t>https://www.scmp.com/tech/big-tech/article/3284168/chinese-state-owned-nuclear-company-claims-breakthrough-radiation-detection-chip</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4377,17 +4429,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>IAEA Annual Report Presented to UN General Assembly</t>
+          <t>Iran Atomic Agency Says It’s Very Unlikely Israel Will Attack Infrastructure Facilities</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Tehran</t>
+        </is>
+      </c>
       <c r="F79" s="2" t="n">
-        <v>45205</v>
+        <v>45566</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -4397,7 +4453,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4407,7 +4463,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/news/2023-iaea-annual-report-presented-to-the-un-general-assembly</t>
+          <t>https://www.timesofisrael.com/liveblog_entry/irans-atomic-agency-says-very-unlikely-israel-will-attack-nuclear-facilities/</t>
         </is>
       </c>
     </row>
@@ -4419,26 +4475,26 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Seychelles Sets Up New Chemical, Biological, Radiological, and Nuclear Team</t>
+          <t>Adurenco signs enrichment contract with French HTGR developer Jimmy</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>45581</v>
+        <v>45422</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -4448,7 +4504,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4458,24 +4514,24 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>http://www.seychellesnewsagency.com/articles/21384/Seychelles+sets+up+new+chemical%2C+biological%2C+radiological+and+nuclear+team</t>
+          <t>https://www.nucnet.org/news/adurenco-signs-enrichment-contract-with-french-htgr-developer-jimmy-10-5-2024</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Columbia Heights Building Fined for Hazardous Conditions After Gas Explosion</t>
+          <t>Amazon Invests in X energy, Unveils SMR Project Plans</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4485,11 +4541,11 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Columbia</t>
+          <t>Washington DC</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>45580</v>
+        <v>45566</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -4509,38 +4565,38 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://thewash.org/2024/10/15/columbia-heights-building-owners-fined-for-hazardous-unsafe-conditions-after-gas-explosion/</t>
+          <t>https://www.world-nuclear-news.org/articles/amazon-invests-in-x-energy-unveils-smr-project-plans</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Explosive</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BRICS members set to increase nuclear energy cooperation</t>
+          <t>Oil Tanker Explosion Fire in Germany</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Brazil, India</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Brasilia, Delhi</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>45392</v>
+        <v>45566</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -4550,7 +4606,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environmental</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4560,7 +4616,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://www.world-nuclear-news.org/articles/brics-members-set-to-increase-nuclear-energy-cooperation</t>
+          <t>https://www.thesun.co.uk/news/31015676/oil-tanker-explosion-fire-germany/</t>
         </is>
       </c>
     </row>
@@ -4572,22 +4628,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US Army Pilots Fly for Lifesaving Chemical Surety Program</t>
+          <t>WHO Warns Parliamentarians Unite to Support Pandemic Agreement</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
@@ -4611,38 +4667,38 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://www.army.mil/article/280511/seasoned_us_army_civilian_pilots_fly_missions_for_lifesaving_chemical_surety_program</t>
+          <t>https://www.who.int/news/item/16-10-2024-parliamentarians-unite-in-berlin-to-sign-global-statement-supporting-the-who-pandemic-agreement</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hazardous Material Leak at Water Treatment Plant in Lebanon County</t>
+          <t>WHO Publishes Cholera Risk Alert for Lebanon</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Lebanon County</t>
+          <t>Beirut</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>45568</v>
+        <v>45566</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -4662,7 +4718,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://local21news.com/news/local/fire-crews-on-scene-of-hazardous-material-leak-at-water-treatment-plant-in-lebanon-county</t>
+          <t>https://www.aa.com.tr/en/europe/who-warns-risk-of-cholera-spread-very-high-in-lebanon/3364359</t>
         </is>
       </c>
     </row>
@@ -4674,26 +4730,26 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Radiological</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>DOE Signs Off on Oklo Fuel Fabrication Facility Design</t>
+          <t>ADCMC Showcases Innovative Digital Initiatives at GITEX 2024</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>45566</v>
+        <v>45580</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -4703,7 +4759,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4713,7 +4769,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://www.world-nuclear-news.org/articles/doe-signs-off-on-oklo-fuel-fabrication-facility-design</t>
+          <t>https://menafn.com/1108780610/ADCMC-showcases-range-of-innovative-digital-initiatives-at-GITEX-Global-2024</t>
         </is>
       </c>
     </row>
@@ -4730,21 +4786,21 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Restart Continues with Shimane 2, Due Back Online in December</t>
+          <t>FANR Board Reviews Barakah Nuclear Plant Regulatory Activities</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Shimane</t>
+          <t>Abu Dhabi</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>45568</v>
+        <v>45566</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -4754,7 +4810,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -4764,34 +4820,34 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://www.nucnet.org/news/restarts-continue-with-shimane-2-due-back-online-in-december-10-3-2024</t>
+          <t>https://www.zawya.com/en/business/energy/fanr-board-reviews-regulatory-activities-at-barakah-approves-agreements-y6opk8sl</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Radiological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chinese State Owned Nuclear Company Claims Breakthrough in Radiation Detection Chip</t>
+          <t>Japan's IAEA News on Fukushima Daiichi Infrastructure Incident</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Fukushima</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
@@ -4805,7 +4861,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -4815,7 +4871,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/big-tech/article/3284168/chinese-state-owned-nuclear-company-claims-breakthrough-radiation-detection-chip</t>
+          <t>https://www3.nhk.or.jp/nhkworld/en/news/20241016_02/</t>
         </is>
       </c>
     </row>
@@ -4827,22 +4883,26 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>WHO Releases Pandemic Preparedness Guidelines</t>
+          <t>UAE Elected Chair of IAEA’s Steering Committee</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
       <c r="F88" s="2" t="n">
-        <v>45566</v>
+        <v>45582</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -4852,7 +4912,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -4862,14 +4922,14 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://www.who.int/publications/i/item/9789240101456</t>
+          <t>https://www.wam.ae/en/article/b5q8w5z-uae-elected-chair-iaeas-steering-committee</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4879,21 +4939,21 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Iran Atomic Agency Says It’s Very Unlikely Israel Will Attack Infrastructure Facilities</t>
+          <t>DOE announces USD900 million funding for Generation III SMR deployment</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Washington DC</t>
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>45566</v>
+        <v>45392</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -4903,7 +4963,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -4913,7 +4973,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://www.timesofisrael.com/liveblog_entry/irans-atomic-agency-says-very-unlikely-israel-will-attack-nuclear-facilities/</t>
+          <t>https://www.nucnet.org/news/doe-announces-usd900-million-funding-for-generation-iii-smr-deployment-10-4-2024</t>
         </is>
       </c>
     </row>
@@ -4930,17 +4990,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Adurenco signs enrichment contract with French HTGR developer Jimmy</t>
+          <t>IAEA begins additional monitoring measures following Japan and China agreement</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
@@ -4954,7 +5014,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -4964,7 +5024,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://www.nucnet.org/news/adurenco-signs-enrichment-contract-with-french-htgr-developer-jimmy-10-5-2024</t>
+          <t>https://www.nucnet.org/news/iaea-begins-additional-monitoring-measures-following-japan-and-china-agreement-10-5-2024</t>
         </is>
       </c>
     </row>
@@ -4981,21 +5041,21 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Amazon Invests in X energy, Unveils SMR Project Plans</t>
+          <t>IAEA begins additional monitoring measures following Japan and China agreement</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>Beijing</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
-        <v>45566</v>
+        <v>45422</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -5005,7 +5065,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5015,38 +5075,38 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://www.world-nuclear-news.org/articles/amazon-invests-in-x-energy-unveils-smr-project-plans</t>
+          <t>https://www.nucnet.org/news/iaea-begins-additional-monitoring-measures-following-japan-and-china-agreement-10-5-2024</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Oil Tanker Explosion Fire in Germany</t>
+          <t>IAEA Director General Statement on situation in Ukraine</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="F92" s="2" t="n">
-        <v>45566</v>
+        <v>45422</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -5056,7 +5116,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5066,7 +5126,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://www.thesun.co.uk/news/31015676/oil-tanker-explosion-fire-germany/</t>
+          <t>https://www.iaea.org/newscenter/pressreleases/update-255-iaea-director-general-statement-on-situation-in-ukraine</t>
         </is>
       </c>
     </row>
@@ -5083,21 +5143,21 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>WHO Warns Parliamentarians Unite to Support Pandemic Agreement</t>
+          <t>Two sheep farms with smallpox infection identified in southern Bulgaria</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Southern Bulgaria</t>
         </is>
       </c>
       <c r="F93" s="2" t="n">
-        <v>45566</v>
+        <v>45392</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -5107,7 +5167,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Animal</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5117,14 +5177,14 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://www.who.int/news/item/16-10-2024-parliamentarians-unite-in-berlin-to-sign-global-statement-supporting-the-who-pandemic-agreement</t>
+          <t>https://www.bta.bg/en/news/economy/763988-two-sheep-farms-with-smallpox-infection-identified-in-southern-bulgaria-in-two-d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5134,17 +5194,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>WHO Publishes Cholera Risk Alert for Lebanon</t>
+          <t>Bird Flu Detected at More Farms in Hungary</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Beirut</t>
+          <t>Budapest</t>
         </is>
       </c>
       <c r="F94" s="2" t="n">
@@ -5158,7 +5218,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Animal</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5168,7 +5228,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://www.aa.com.tr/en/europe/who-warns-risk-of-cholera-spread-very-high-in-lebanon/3364359</t>
+          <t>https://dailynewshungary.com/bird-flu-detected-at-more-farms-in-hungary/</t>
         </is>
       </c>
     </row>
@@ -5180,26 +5240,26 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Radiological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ADCMC Showcases Innovative Digital Initiatives at GITEX 2024</t>
+          <t>Japanese Data Centre Seeks Nuclear Electricity Supplies</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>45580</v>
+        <v>45422</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -5219,7 +5279,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://menafn.com/1108780610/ADCMC-showcases-range-of-innovative-digital-initiatives-at-GITEX-Global-2024</t>
+          <t>https://www.world-nuclear-news.org/articles/japanese-data-centre-seeks-nuclear-electricity-supplies</t>
         </is>
       </c>
     </row>
@@ -5231,26 +5291,26 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FANR Board Reviews Barakah Nuclear Plant Regulatory Activities</t>
+          <t>WHO working to stop cholera spread amid conflict in Lebanon</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Beirut</t>
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>45566</v>
+        <v>45582</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -5270,14 +5330,14 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://www.zawya.com/en/business/energy/fanr-board-reviews-regulatory-activities-at-barakah-approves-agreements-y6opk8sl</t>
+          <t>https://www.who.int/news/item/17-10-2024-who-in-lebanon-working-to-stop-cholera-spread-amid-conflict</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5287,17 +5347,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Japan's IAEA News on Fukushima Daiichi Infrastructure Incident</t>
+          <t>Framatome to Supply Hungarian Plant with Nuclear Fuel</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Fukushima</t>
+          <t>Budapest</t>
         </is>
       </c>
       <c r="F97" s="2" t="n">
@@ -5311,7 +5371,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5321,7 +5381,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>https://www3.nhk.or.jp/nhkworld/en/news/20241016_02/</t>
+          <t>https://www.world-nuclear-news.org/articles/framatome-to-supply-hungarian-plant-with-nuclear-fuel</t>
         </is>
       </c>
     </row>
@@ -5338,21 +5398,21 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>UAE Elected Chair of IAEA’s Steering Committee</t>
+          <t>IAEA mission recognizes Latvia’s commitment to improve nuclear safety</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>45582</v>
+        <v>45422</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -5362,7 +5422,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5372,7 +5432,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>https://www.wam.ae/en/article/b5q8w5z-uae-elected-chair-iaeas-steering-committee</t>
+          <t>https://www.iaea.org/newscenter/pressreleases/iaea-mission-recognizes-latvias-commitment-to-improve-nuclear-and-radiation-safety-encourages-continued-improvements</t>
         </is>
       </c>
     </row>
@@ -5389,17 +5449,21 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Agency plans next workshops in bid to advance nuclear in Europe and Eurasia</t>
+          <t>Tritium level far below Japan’s operational limit in 10th batch of ALPS treated water</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr"/>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Fukushima</t>
+        </is>
+      </c>
       <c r="F99" s="2" t="n">
-        <v>45392</v>
+        <v>45422</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -5409,7 +5473,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Environmental</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5419,7 +5483,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>https://www.nucnet.org/news/agency-plans-next-workshops-in-bid-to-advance-nuclear-inn-europe-and-eurasia-10-4-2024</t>
+          <t>https://www.iaea.org/newscenter/pressreleases/tritium-level-far-below-japans-operational-limit-in-tenth-batch-of-alps-treated-water-iaea-confirms</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5500,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Alliance calls for commission to fully recognize nuclear in paradigm policy shift</t>
+          <t>Setting the Agenda: Regional Cooperative Agreement representatives convene at IAEA</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5444,9 +5508,13 @@
           <t>International</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
       <c r="F100" s="2" t="n">
-        <v>45392</v>
+        <v>45422</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -5456,7 +5524,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5466,38 +5534,38 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>https://www.nucnet.org/news/alliance-calls-for-commission-to-fully-recognise-nuclear-in-paradigm-policy-shift-10-4-2024</t>
+          <t>https://www.iaea.org/newscenter/news/setting-the-agenda-regional-cooperative-agreement-representatives-convene-at-iaea-general-conference-to-review-activities-establish-priorities</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Explosive</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>DOE announces USD900 million funding for Generation III SMR deployment</t>
+          <t>Possible targets in Iran: Economic, nuclear, and regime infrastructure</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>45392</v>
+        <v>45573</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -5507,7 +5575,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -5517,7 +5585,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>https://www.nucnet.org/news/doe-announces-usd900-million-funding-for-generation-iii-smr-deployment-10-4-2024</t>
+          <t>https://www.fdd.org/analysis/2024/10/08/possible-targets-in-iran-Economic-nuclear-and-regime-infrastructure/</t>
         </is>
       </c>
     </row>
@@ -5534,17 +5602,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>IAEA begins additional monitoring measures following Japan and China agreement</t>
+          <t>IAEA to hold international conference on Small Modular Reactors</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Japan, China</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Tokyo, Beijing</t>
+          <t>Vienna</t>
         </is>
       </c>
       <c r="F102" s="2" t="n">
@@ -5558,7 +5626,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5568,7 +5636,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>https://www.nucnet.org/news/iaea-begins-additional-monitoring-measures-following-japan-and-china-agreement-10-5-2024</t>
+          <t>https://www.iaea.org/newscenter/news/international-conference-on-small-modular-reactors-next-week</t>
         </is>
       </c>
     </row>
@@ -5585,21 +5653,21 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>IAEA Director General Statement on situation in Ukraine</t>
+          <t>Japan shifting back to nuclear to ditch coal power</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>45422</v>
+        <v>45566</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -5609,7 +5677,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -5619,38 +5687,38 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/pressreleases/update-255-iaea-director-general-statement-on-situation-in-ukraine</t>
+          <t>https://business.inquirer.net/485687/japan-shifting-back-to-nuclear-to-ditch-coal-power-ai</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Two sheep farms with smallpox infection identified in southern Bulgaria</t>
+          <t>Fire breaks out at Oxford's Tull Chemical Company</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Southern Bulgaria</t>
+          <t>Oxford</t>
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>45392</v>
+        <v>45566</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -5660,7 +5728,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Animal</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -5670,7 +5738,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>https://www.bta.bg/en/news/economy/763988-two-sheep-farms-with-smallpox-infection-identified-in-southern-bulgaria-in-two-d</t>
+          <t>https://www.al.com/news/2024/10/fire-breaks-out-at-oxfords-tull-chemical-company.html</t>
         </is>
       </c>
     </row>
@@ -5687,17 +5755,21 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>WHO Publication on health information (disease data)</t>
+          <t>Regional leaders agree to improve health financing, prioritize digital health</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
+          <t>Macao</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Macau</t>
+        </is>
+      </c>
       <c r="F105" s="2" t="n">
-        <v>45392</v>
+        <v>45589</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -5717,34 +5789,34 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>https://www.who.int/publications/i/item/9789240098619</t>
+          <t>https://www.who.int/macaochina/news/detail-wpro/24-10-2024-regional-health-leaders-agree-to-improve-financing-to-achieve-universal-health-coverage--prioritize-digital-health</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bird Flu Detected at More Farms in Hungary</t>
+          <t>Morocco hosts international conference on AI and Chemical Weapons Convention</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Budapest</t>
+          <t>Rabat</t>
         </is>
       </c>
       <c r="F106" s="2" t="n">
@@ -5758,7 +5830,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Animal</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -5768,7 +5840,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>https://dailynewshungary.com/bird-flu-detected-at-more-farms-in-hungary/</t>
+          <t>https://www.fananews.com/language/en/morocco-hosts-international-conference-on-ai-chemical-weapons-convention-in-partnership-with-organisation-for-prohibition-of-chemical-weapons/</t>
         </is>
       </c>
     </row>
@@ -5785,17 +5857,21 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Small Modular Reactors Advances in SMR Developments</t>
+          <t>Jordan is poised to secure funding for managing chemical and nuclear waste</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Amman</t>
+        </is>
+      </c>
       <c r="F107" s="2" t="n">
-        <v>2024</v>
+        <v>45585</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -5815,7 +5891,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/publications/15790/small-modular-reactors-advances-in-smr-developments-2024</t>
+          <t>https://menafn.com/arabic/1108798677/%D8%A7%D9%84%D8%A7%D9%94%D8%B1%D8%AF%D9%86-%D9%85%D9%88%D9%94%D9%87%D9%84-%D9%84%D9%84%D8%AD%D8%B5%D9%88%D9%84-%D8%B9%D9%84%D9%89-%D8%AA%D9%85%D9%88%D9%8A%D9%84-%D9%84%D8%A7%D9%95%D8%AF%D8%A7%D8%B1%D8%A9-%D8%A7%D9%84%D9%85%D9%88%D8%A7%D8%AF-%D8%A7%D9%84%D9%83%D9%8A%D9%85%D9%8A%D8%A7%D9%8A%D9%94%D9%8A%D8%A9-%D9%88%D8%A7%D9%84%D9%86%D9%81%D8%A7%D9%8A%D8%A7%D8%AA</t>
         </is>
       </c>
     </row>
@@ -5832,21 +5908,21 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Japanese Data Centre Seeks Nuclear Electricity Supplies</t>
+          <t>Uganda delegation commends Kenya’s radiation safety</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>45422</v>
+        <v>45566</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -5856,7 +5932,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -5866,7 +5942,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>https://www.world-nuclear-news.org/articles/japanese-data-centre-seeks-nuclear-electricity-supplies</t>
+          <t>https://www.standardmedia.co.ke/health/counties/article/2001439117/uganda-delegation-commends-kenyas-radiation-safety</t>
         </is>
       </c>
     </row>
@@ -5883,21 +5959,21 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>WHO working to stop cholera spread amid conflict in Lebanon</t>
+          <t>South Sudan faces severe flooding compounding health crisis</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Beirut</t>
+          <t>Juba</t>
         </is>
       </c>
       <c r="F109" s="2" t="n">
-        <v>45582</v>
+        <v>45566</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -5917,7 +5993,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>https://www.who.int/news/item/17-10-2024-who-in-lebanon-working-to-stop-cholera-spread-amid-conflict</t>
+          <t>https://www.afro.who.int/countries/south-sudan/news/severe-flooding-compounds-health-crisis-south-sudan</t>
         </is>
       </c>
     </row>
@@ -5929,26 +6005,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Framatome to Supply Hungarian Plant with Nuclear Fuel</t>
+          <t>Vietnam eliminates trachoma as a human problem</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Budapest</t>
+          <t>Hanoi</t>
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>45566</v>
+        <v>45586</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -5958,7 +6034,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -5968,38 +6044,38 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>https://www.world-nuclear-news.org/articles/framatome-to-supply-hungarian-plant-with-nuclear-fuel</t>
+          <t>https://www.who.int/news/item/21-10-2024-viet-nam-eliminates-trachoma-as-a-public-health-problem</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>IAEA mission recognizes Latvia’s commitment to improve nuclear safety</t>
+          <t>Mosquito borne virus Triple E continues its spread, worrying state health officials</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>New Hampshire</t>
         </is>
       </c>
       <c r="F111" s="2" t="n">
-        <v>45422</v>
+        <v>45566</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -6019,7 +6095,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/pressreleases/iaea-mission-recognizes-latvias-commitment-to-improve-nuclear-and-radiation-safety-encourages-continued-improvements</t>
+          <t>https://newhampshirebulletin.com/2024/10/21/the-mosquito-borne-virus-triple-e-continues-its-spread-worrying-state-health-officials/</t>
         </is>
       </c>
     </row>
@@ -6036,21 +6112,21 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tritium level far below Japan’s operational limit in 10th batch of ALPS treated water</t>
+          <t>Eritrea signs third country programme framework (CPF)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Eritrea</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Fukushima</t>
+          <t>Asmara</t>
         </is>
       </c>
       <c r="F112" s="2" t="n">
-        <v>45422</v>
+        <v>45566</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -6060,7 +6136,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6070,7 +6146,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/pressreleases/tritium-level-far-below-japans-operational-limit-in-tenth-batch-of-alps-treated-water-iaea-confirms</t>
+          <t>https://www.iaea.org/newscenter/news/the-state-of-eritrea-signs-its-third-country-programme-framework-cpf-for-2024-2028</t>
         </is>
       </c>
     </row>
@@ -6087,21 +6163,21 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Setting the Agenda: Regional Cooperative Agreement representatives convene at IAEA</t>
+          <t>Serbia continues discussions on future nuclear projects</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Vienna</t>
+          <t>Belgrade</t>
         </is>
       </c>
       <c r="F113" s="2" t="n">
-        <v>45422</v>
+        <v>45566</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -6111,7 +6187,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6121,24 +6197,24 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/news/setting-the-agenda-regional-cooperative-agreement-representatives-convene-at-iaea-general-conference-to-review-activities-establish-priorities</t>
+          <t>https://www.world-nuclear-news.org/articles/serbia-continues-discussions-on-future-nuclear-projects</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Possible targets in Iran: Economic, nuclear, and regime infrastructure</t>
+          <t>Iran may reassess nuclear policies if sites are attacked</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6152,7 +6228,7 @@
         </is>
       </c>
       <c r="F114" s="2" t="n">
-        <v>45573</v>
+        <v>45566</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -6162,7 +6238,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -6172,7 +6248,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>https://www.fdd.org/analysis/2024/10/08/possible-targets-in-iran-Economic-nuclear-and-regime-infrastructure/</t>
+          <t>https://www.tehrantimes.com/news/505287/Iran-may-reassess-nuclear-policies-if-sites-are-attacked-source</t>
         </is>
       </c>
     </row>
@@ -6184,26 +6260,26 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>IAEA to hold international conference on Small Modular Reactors</t>
+          <t>Ombudsman condemns European Commission for failing to control hazardous chemicals</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Vienna</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="F115" s="2" t="n">
-        <v>45422</v>
+        <v>45586</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -6213,7 +6289,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6223,7 +6299,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/news/international-conference-on-small-modular-reactors-next-week</t>
+          <t>https://www.sustainableviews.com/ombudsman-condemns-european-commission-for-failing-to-control-hazardous-chemicals-44927379/</t>
         </is>
       </c>
     </row>
@@ -6235,22 +6311,26 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Radiological, Nuclear</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>New Coordinated Research Project CRP optimizing mining wastewater remediation</t>
+          <t>Ombudsman condemns European Commission for failing to control hazardous chemicals</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
       <c r="F116" s="2" t="n">
-        <v>45582</v>
+        <v>45586</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -6260,7 +6340,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6270,7 +6350,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/news/new-coordinated-research-project-crp-optimizing-mining-wastewater-remediation</t>
+          <t>https://www.sustainableviews.com/ombudsman-condemns-european-commission-for-failing-to-control-hazardous-chemicals-44927379/</t>
         </is>
       </c>
     </row>
@@ -6282,26 +6362,26 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Japan shifting back to nuclear to ditch coal power</t>
+          <t>Ombudsman condemns European Commission for failing to control hazardous chemicals</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Moscow</t>
         </is>
       </c>
       <c r="F117" s="2" t="n">
-        <v>45566</v>
+        <v>45586</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -6311,7 +6391,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -6321,34 +6401,34 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>https://business.inquirer.net/485687/japan-shifting-back-to-nuclear-to-ditch-coal-power-ai</t>
+          <t>https://www.sustainableviews.com/ombudsman-condemns-european-commission-for-failing-to-control-hazardous-chemicals-44927379/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Fire breaks out at Oxford's Tull Chemical Company</t>
+          <t>Killer diseases put focus on Kenya’s healthcare</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Oxford</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="F118" s="2" t="n">
@@ -6372,7 +6452,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>https://www.al.com/news/2024/10/fire-breaks-out-at-oxfords-tull-chemical-company.html</t>
+          <t>https://www.zawya.com/en/business/healthcare/killer-diseases-put-focus-on-kenyas-health-care-iqx0b5qc</t>
         </is>
       </c>
     </row>
@@ -6384,26 +6464,26 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Regional leaders agree to improve health financing, prioritize digital health</t>
+          <t>China issues operation license for Unit 1 of Zhangzhou Nuclear Plant</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Macao</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Macau</t>
+          <t>Zhangzhou</t>
         </is>
       </c>
       <c r="F119" s="2" t="n">
-        <v>45589</v>
+        <v>45566</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -6413,7 +6493,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -6423,7 +6503,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>https://www.who.int/macaochina/news/detail-wpro/24-10-2024-regional-health-leaders-agree-to-improve-financing-to-achieve-universal-health-coverage--prioritize-digital-health</t>
+          <t>https://www.enerdata.net/publications/daily-energy-news/china-issues-operation-licence-unit-1-zhangzhou-nuclear-plant.html</t>
         </is>
       </c>
     </row>
@@ -6435,26 +6515,26 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Morocco hosts international conference on AI and Chemical Weapons Convention</t>
+          <t>Saudi Arabia announces $13B investments in healthcare sector during Global Health Expo</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Rabat</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="F120" s="2" t="n">
-        <v>45566</v>
+        <v>45594</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -6474,38 +6554,38 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>https://www.fananews.com/language/en/morocco-hosts-international-conference-on-ai-chemical-weapons-convention-in-partnership-with-organisation-for-prohibition-of-chemical-weapons/</t>
+          <t>https://gulfnews.com/business/markets/investments-of-13b-in-saudi-arabias-healthcare-sector-unveil-during-global-health-exhibition-in-riyadh-1.1729589734070</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Jordan is poised to secure funding for managing chemical and nuclear waste</t>
+          <t>Bird flu confirmed in Washington State</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Amman</t>
+          <t>Washington DC</t>
         </is>
       </c>
       <c r="F121" s="2" t="n">
-        <v>45585</v>
+        <v>45578</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -6515,7 +6595,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Animal</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -6525,7 +6605,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>https://menafn.com/arabic/1108798677/%D8%A7%D9%84%D8%A7%D9%94%D8%B1%D8%AF%D9%86-%D9%85%D9%88%D9%94%D9%87%D9%84-%D9%84%D9%84%D8%AD%D8%B5%D9%88%D9%84-%D8%B9%D9%84%D9%89-%D8%AA%D9%85%D9%88%D9%8A%D9%84-%D9%84%D8%A7%D9%95%D8%AF%D8%A7%D8%B1%D8%A9-%D8%A7%D9%84%D9%85%D9%88%D8%A7%D8%AF-%D8%A7%D9%84%D9%83%D9%8A%D9%85%D9%8A%D8%A7%D9%8A%D9%94%D9%8A%D8%A9-%D9%88%D8%A7%D9%84%D9%86%D9%81%D8%A7%D9%8A%D8%A7%D8%AA</t>
+          <t>https://www.fox13seattle.com/news/bird-flu-wa</t>
         </is>
       </c>
     </row>
@@ -6537,22 +6617,22 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Uganda delegation commends Kenya’s radiation safety</t>
+          <t>Hazardous waste containers arrive in Durres on Sunday</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Albania</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Durres</t>
         </is>
       </c>
       <c r="F122" s="2" t="n">
@@ -6566,7 +6646,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Environmental</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -6576,7 +6656,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>https://www.standardmedia.co.ke/health/counties/article/2001439117/uganda-delegation-commends-kenyas-radiation-safety</t>
+          <t>https://telegrafi.com/en/hazardous-waste-containers-arrive-in-Durres-on-Sunday/</t>
         </is>
       </c>
     </row>
@@ -6593,17 +6673,17 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>South Sudan faces severe flooding compounding health crisis</t>
+          <t>WHO confirms Vietnam has eliminated trachoma</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Juba</t>
+          <t>Hanoi</t>
         </is>
       </c>
       <c r="F123" s="2" t="n">
@@ -6627,7 +6707,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>https://www.afro.who.int/countries/south-sudan/news/severe-flooding-compounds-health-crisis-south-sudan</t>
+          <t>https://asianews.network/who-confirms-vietnam-has-eliminated-trachoma/</t>
         </is>
       </c>
     </row>
@@ -6644,21 +6724,21 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Vietnam eliminates trachoma as a human problem</t>
+          <t>UAE increases health funding amidst economic diversification effort</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Hanoi</t>
+          <t>Abu Dhabi</t>
         </is>
       </c>
       <c r="F124" s="2" t="n">
-        <v>45586</v>
+        <v>45566</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -6668,7 +6748,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -6678,14 +6758,14 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>https://www.who.int/news/item/21-10-2024-viet-nam-eliminates-trachoma-as-a-public-health-problem</t>
+          <t>https://healthcareasiamagazine.com/healthcare/news/uae-increases-health-funding-amidst-economic-diversification-effort</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -6695,21 +6775,21 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Mosquito borne virus Triple E continues its spread, worrying state health officials</t>
+          <t>Ministry of Health Annual Report for the year ended 30 June 2024</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>New Hampshire</t>
+          <t>Wellington</t>
         </is>
       </c>
       <c r="F125" s="2" t="n">
-        <v>45566</v>
+        <v>45473</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -6729,7 +6809,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>https://newhampshirebulletin.com/2024/10/21/the-mosquito-borne-virus-triple-e-continues-its-spread-worrying-state-health-officials/</t>
+          <t>https://www.health.govt.nz/publications/ministry-of-health-annual-report-for-the-year-ended-30-june-2024</t>
         </is>
       </c>
     </row>
@@ -6741,22 +6821,26 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Investment in nuclear must rapidly increase to USD125 billion a year</t>
+          <t>ABHI UK Pavilion highlights transformative HealthTech innovations at Global Health Expo</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
       <c r="F126" s="2" t="n">
-        <v>45301</v>
+        <v>45566</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -6776,7 +6860,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>https://www.nucnet.org/news/investment-in-nuclear-must-rapidly-increase-to-usd125-billion-a-year-10-1-2024</t>
+          <t>https://www.zawya.com/en/press-release/events-and-conferences/abhi-uk-pavilion-highlights-transformative-healthtech-innovations-at-global-health-exhibition-in-saudi-arabia-b8l3ocfl</t>
         </is>
       </c>
     </row>
@@ -6788,26 +6872,26 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Eritrea signs third country programme framework (CPF)</t>
+          <t>Healthcare Future Summit 2024 in UAE</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Eritrea</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Asmara</t>
+          <t>Abu Dhabi</t>
         </is>
       </c>
       <c r="F127" s="2" t="n">
-        <v>45566</v>
+        <v>45586</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -6827,7 +6911,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/news/the-state-of-eritrea-signs-its-third-country-programme-framework-cpf-for-2024-2028</t>
+          <t>https://mediaoffice.ae/en/news/2024/october/21-10/healthcare-future-summit-2024</t>
         </is>
       </c>
     </row>
@@ -6839,26 +6923,26 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia continues discussions on future nuclear projects</t>
+          <t>Leaked EU budget plans spark fears for health budget cuts</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Belgrade</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="F128" s="2" t="n">
-        <v>45566</v>
+        <v>45587</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -6878,7 +6962,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>https://www.world-nuclear-news.org/articles/serbia-continues-discussions-on-future-nuclear-projects</t>
+          <t>https://www.euronews.com/health/2024/10/22/leaked-budget-plans-spark-fears-for-eu-health-budget</t>
         </is>
       </c>
     </row>
@@ -6890,26 +6974,26 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Iran may reassess nuclear policies if sites are attacked</t>
+          <t>Leaked EU budget plans spark fears for health budget cuts</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F129" s="2" t="n">
-        <v>45566</v>
+        <v>45587</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -6919,7 +7003,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -6929,7 +7013,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>https://www.tehrantimes.com/news/505287/Iran-may-reassess-nuclear-policies-if-sites-are-attacked-source</t>
+          <t>https://www.euronews.com/health/2024/10/22/leaked-budget-plans-spark-fears-for-eu-health-budget</t>
         </is>
       </c>
     </row>
@@ -6941,26 +7025,26 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ombudsman condemns European Commission for failing to control hazardous chemicals</t>
+          <t>Leaked EU budget plans spark fears for health budget cuts</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Germany, France, Russia</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Berlin, Paris, Moscow</t>
+          <t>Moscow</t>
         </is>
       </c>
       <c r="F130" s="2" t="n">
-        <v>45586</v>
+        <v>45587</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -6970,7 +7054,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -6980,14 +7064,14 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>https://www.sustainableviews.com/ombudsman-condemns-european-commission-for-failing-to-control-hazardous-chemicals-44927379/</t>
+          <t>https://www.euronews.com/health/2024/10/22/leaked-budget-plans-spark-fears-for-eu-health-budget</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -6997,17 +7081,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Killer diseases put focus on Kenya’s healthcare</t>
+          <t>Dengue cases surge with 97 new infections reported</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Nairobi</t>
+          <t>Islamabad</t>
         </is>
       </c>
       <c r="F131" s="2" t="n">
@@ -7031,7 +7115,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>https://www.zawya.com/en/business/healthcare/killer-diseases-put-focus-on-kenyas-health-care-iqx0b5qc</t>
+          <t>https://www.app.com.pk/domestic/dengue-cases-surge-with-97-new-infections-reported/</t>
         </is>
       </c>
     </row>
@@ -7043,26 +7127,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>China issues operation license for Unit 1 of Zhangzhou Nuclear Plant</t>
+          <t>UK rivers are contaminated by harmful chemicals and pollutants</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Zhangzhou</t>
+          <t>London</t>
         </is>
       </c>
       <c r="F132" s="2" t="n">
-        <v>45566</v>
+        <v>45586</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -7072,7 +7156,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environmental</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7082,38 +7166,38 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>https://www.enerdata.net/publications/daily-energy-news/china-issues-operation-licence-unit-1-zhangzhou-nuclear-plant.html</t>
+          <t>https://www.theguardian.com/environment/2024/oct/21/uk-rivers-chemicals-stimulants-phosphates-nintrate-endangering-aquatic-life</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Saudi Arabia announces $13B investments in healthcare sector during Global Health Expo</t>
+          <t>Air quality in Lahore drops to hazardous levels</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Lahore</t>
         </is>
       </c>
       <c r="F133" s="2" t="n">
-        <v>45594</v>
+        <v>45566</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -7123,7 +7207,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -7133,7 +7217,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>https://gulfnews.com/business/markets/investments-of-13b-in-saudi-arabias-healthcare-sector-unveil-during-global-health-exhibition-in-riyadh-1.1729589734070</t>
+          <t>https://www.thenews.com.pk/latest/1242702-air-quality-in-lahore-drops-to-hazardous</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7229,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bird flu confirmed in Washington State</t>
+          <t>Federal lawsuit filed against Biolab for chemical release and fire</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -7164,7 +7248,7 @@
         </is>
       </c>
       <c r="F134" s="2" t="n">
-        <v>45578</v>
+        <v>45566</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -7174,7 +7258,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Animal</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -7184,7 +7268,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>https://www.fox13seattle.com/news/bird-flu-wa</t>
+          <t>https://www.powderbulksolids.com/industrial-fires-explosions/federal-lawsuit-filed-against-biolab-for-chemical-release-fire</t>
         </is>
       </c>
     </row>
@@ -7201,21 +7285,21 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Hazardous waste containers arrive in Durres on Sunday</t>
+          <t>OPCW Associate Programme concludes in The Hague</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Albania</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Durres</t>
+          <t>The Hague</t>
         </is>
       </c>
       <c r="F135" s="2" t="n">
-        <v>45566</v>
+        <v>45589</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -7225,7 +7309,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -7235,34 +7319,34 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>https://telegrafi.com/en/hazardous-waste-containers-arrive-in-Durres-on-Sunday/</t>
+          <t>https://www.opcw.org/media-centre/news/2024/10/2024-opcw-associate-programme-concludes-hague</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>WHO confirms Vietnam has eliminated trachoma</t>
+          <t>Iran warns IAEA about threats to nuclear sites from Zionist entity</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Hanoi</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F136" s="2" t="n">
@@ -7286,34 +7370,34 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>https://asianews.network/who-confirms-vietnam-has-eliminated-trachoma/</t>
+          <t>https://al24news.com/en/iran-warns-iaea-about-zionist-entity-threats-to-nuclear-sites/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>UAE increases health funding amidst economic diversification effort</t>
+          <t>North Korea Gets Nuclear Help From Russia in Exchange</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>North Korea</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Pyongyang</t>
         </is>
       </c>
       <c r="F137" s="2" t="n">
@@ -7327,7 +7411,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -7337,7 +7421,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>https://healthcareasiamagazine.com/healthcare/news/uae-increases-health-funding-amidst-economic-diversification-effort</t>
+          <t>https://regtechtimes.com/north-korea-gets-nuclear-help-from-russia-in-exch/</t>
         </is>
       </c>
     </row>
@@ -7349,26 +7433,26 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ministry of Health Annual Report for the year ended 30 June 2024</t>
+          <t>Abu Dhabi's DOH Unveils Sahatna Platform for Proactive Health Management</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Wellington</t>
+          <t>Abu Dhabi</t>
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>45473</v>
+        <v>45566</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -7388,7 +7472,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>https://www.health.govt.nz/publications/ministry-of-health-annual-report-for-the-year-ended-30-june-2024</t>
+          <t>https://healthcareasiamagazine.com/healthcare/news/abu-dhabis-doh-unveils-sahatna-platform-proactive-health-mgmt</t>
         </is>
       </c>
     </row>
@@ -7400,22 +7484,22 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ABHI UK Pavilion highlights transformative HealthTech innovations at Global Health Expo</t>
+          <t>Bahrain Health Minister Discusses Health Cooperation With Egyptian Counterpart</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Manama</t>
         </is>
       </c>
       <c r="F139" s="2" t="n">
@@ -7429,7 +7513,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -7439,38 +7523,38 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>https://www.zawya.com/en/press-release/events-and-conferences/abhi-uk-pavilion-highlights-transformative-healthtech-innovations-at-global-health-exhibition-in-saudi-arabia-b8l3ocfl</t>
+          <t>https://www.bna.bh/en/HealthMinisterdiscusseshealthcooperationwithEgyptiancounterpart.aspx?cms=q8FmFJgiscL2fwIzON1%2BDgvZcgSkeUomlF7ra61uAvQ%3D</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Healthcare Future Summit 2024 in UAE</t>
+          <t>Israel Arrests 7 Jerusalem Residents Allegedly Plotting Attacks for Iran</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Jerusalem</t>
         </is>
       </c>
       <c r="F140" s="2" t="n">
-        <v>45586</v>
+        <v>45566</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -7480,7 +7564,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -7490,7 +7574,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>https://mediaoffice.ae/en/news/2024/october/21-10/healthcare-future-summit-2024</t>
+          <t>https://economictimes.indiatimes.com/news/international/world-news/tried-to-kill-nuclear-scientist-israel-arrests-7-jerusalem-residents-allegedly-plotting-attacks-for-iran/videoshow/114474179.cms?from=mdr</t>
         </is>
       </c>
     </row>
@@ -7502,26 +7586,26 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Leaked EU budget plans spark fears for health budget cuts</t>
+          <t>Mississippi Hosts Summit on Future Nuclear Power in the State</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Germany, France, Russia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Berlin, Paris, Moscow</t>
+          <t>Jackson</t>
         </is>
       </c>
       <c r="F141" s="2" t="n">
-        <v>45587</v>
+        <v>45588</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -7541,34 +7625,34 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>https://www.euronews.com/health/2024/10/22/leaked-budget-plans-spark-fears-for-eu-health-budget</t>
+          <t>https://www.wlbt.com/2024/10/23/mississippi-public-service-commission-hosts-summit-future-nuclear-power-state/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Dengue cases surge with 97 new infections reported</t>
+          <t>Bahrain Health Minister Participates in PHDC Global Conference</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Islamabad</t>
+          <t>Manama</t>
         </is>
       </c>
       <c r="F142" s="2" t="n">
@@ -7592,7 +7676,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>https://www.app.com.pk/domestic/dengue-cases-surge-with-97-new-infections-reported/</t>
+          <t>https://www.bna.bh/en/HealthMinisterparticipatesinPHDCGlobalConference.aspx?cms=q8FmFJgiscL2fwIzON1%2BDnw8CXsPMB0KW78z%2FqJE8w8%3D</t>
         </is>
       </c>
     </row>
@@ -7604,26 +7688,26 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>UK rivers are contaminated by harmful chemicals and pollutants</t>
+          <t>Putin Erdogan to Discuss Nuclear Power Plants and Gas Hub on Sidelines of BRICS Summit</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Moscow</t>
         </is>
       </c>
       <c r="F143" s="2" t="n">
-        <v>45586</v>
+        <v>45588</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -7633,7 +7717,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -7643,34 +7727,34 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/environment/2024/oct/21/uk-rivers-chemicals-stimulants-phosphates-nintrate-endangering-aquatic-life</t>
+          <t>https://english.alarabiya.net/News/world/2024/10/23/putin-erdogan-to-discuss-nuclear-power-plants-gas-hub-on-sidelines-of-brics-</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Air quality in Lahore drops to hazardous levels</t>
+          <t>Reactor Assembly Completed for Bangladesh’s First Nuclear Plant</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Lahore</t>
+          <t>Dhaka</t>
         </is>
       </c>
       <c r="F144" s="2" t="n">
@@ -7684,7 +7768,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -7694,34 +7778,34 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>https://www.thenews.com.pk/latest/1242702-air-quality-in-lahore-drops-to-hazardous</t>
+          <t>https://www.world-nuclear-news.org/articles/reactor-assembly-completed-for-bangladeshs-first-nuclear-plant</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Federal lawsuit filed against Biolab for chemical release and fire</t>
+          <t>India Launches Fourth Nuclear Submarine into Water</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F145" s="2" t="n">
@@ -7735,7 +7819,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -7745,7 +7829,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>https://www.powderbulksolids.com/industrial-fires-explosions/federal-lawsuit-filed-against-biolab-for-chemical-release-fire</t>
+          <t>https://www.thehindu.com/news/national/indias-fourth-nuclear-submarine-launched-into-water/article68783731.ece</t>
         </is>
       </c>
     </row>
@@ -7757,26 +7841,26 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>OPCW Associate Programme concludes in The Hague</t>
+          <t>Latvia Improves Nuclear Safety Infrastructure</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>The Hague</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F146" s="2" t="n">
-        <v>45589</v>
+        <v>45566</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -7786,7 +7870,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -7796,14 +7880,14 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>https://www.opcw.org/media-centre/news/2024/10/2024-opcw-associate-programme-concludes-hague</t>
+          <t>https://www.neimagazine.com/news/latvia-improves-nuclear-safety-infrastructure/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -7813,17 +7897,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Iran warns IAEA about threats to nuclear sites from Zionist entity</t>
+          <t>Qatar Reaffirms Commitment to Nuclear Non Proliferation</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Doha</t>
         </is>
       </c>
       <c r="F147" s="2" t="n">
@@ -7847,14 +7931,14 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>https://al24news.com/en/iran-warns-iaea-about-zionist-entity-threats-to-nuclear-sites/</t>
+          <t>https://www.gulf-times.com/article/693061/qatar/qatar-reaffirms-commitment-to-continuing-efforts-toward-elimination-of-nuclear-weapons-and-nuclear-non-proliferation</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -7864,17 +7948,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>North Korea Gets Nuclear Help From Russia in Exchange</t>
+          <t>UK Nuclear Transport Ship to Test Rigid Sail Technology</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>North Korea</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Pyongyang</t>
+          <t>London</t>
         </is>
       </c>
       <c r="F148" s="2" t="n">
@@ -7888,7 +7972,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -7898,7 +7982,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>https://regtechtimes.com/north-korea-gets-nuclear-help-from-russia-in-exch/</t>
+          <t>https://maritime-executive.com/article/nuclear-transport-ship-to-test-uk-s-first-rigid-sail</t>
         </is>
       </c>
     </row>
@@ -7910,22 +7994,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Abu Dhabi's DOH Unveils Sahatna Platform for Proactive Health Management</t>
+          <t>CBRNE Training Conference Focuses on Organizational and Clinical Aspects</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="F149" s="2" t="n">
@@ -7949,34 +8033,34 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>https://healthcareasiamagazine.com/healthcare/news/abu-dhabis-doh-unveils-sahatna-platform-proactive-health-mgmt</t>
+          <t>https://web.uniroma2.it/it/contenuto/eventi-cbrne-aspetti-organizzativi-e-clinici-il-convegno-per-la-formazione</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Bahrain Health Minister Discusses Health Cooperation With Egyptian Counterpart</t>
+          <t>Iran Submits Protest Note to IAEA Over Israeli Threats to Nuclear Sites</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Manama</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
@@ -8000,34 +8084,34 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>https://www.bna.bh/en/HealthMinisterdiscusseshealthcooperationwithEgyptiancounterpart.aspx?cms=q8FmFJgiscL2fwIzON1%2BDgvZcgSkeUomlF7ra61uAvQ%3D</t>
+          <t>https://www.aa.com.tr/en/energy/nuclear/iran-submits-protest-note-to-iaea-over-israeli-threats-to-nuclear-sites/44088?amp=1</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Israel Arrests 7 Jerusalem Residents Allegedly Plotting Attacks for Iran</t>
+          <t>SDAIA and Saudi Health Ministry Agree to Manage National Health Data</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Jerusalem</t>
+          <t>Riyadh</t>
         </is>
       </c>
       <c r="F151" s="2" t="n">
@@ -8051,7 +8135,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>https://economictimes.indiatimes.com/news/international/world-news/tried-to-kill-nuclear-scientist-israel-arrests-7-jerusalem-residents-allegedly-plotting-attacks-for-iran/videoshow/114474179.cms?from=mdr</t>
+          <t>https://www.zawya.com/en/business/healthcare/sdaia-and-health-ministry-agree-to-cooperate-in-managing-national-data-in-saudi-health-sector-p7a9n4fv</t>
         </is>
       </c>
     </row>
@@ -8068,21 +8152,21 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Mississippi Hosts Summit on Future Nuclear Power in the State</t>
+          <t>Azerbaijan's Nuclear Project Supports Regional Energy Integration</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Jackson</t>
+          <t>Baku</t>
         </is>
       </c>
       <c r="F152" s="2" t="n">
-        <v>45588</v>
+        <v>45566</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -8102,7 +8186,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>https://www.wlbt.com/2024/10/23/mississippi-public-service-commission-hosts-summit-future-nuclear-power-state/</t>
+          <t>https://en.trend.az/business/3960432.html</t>
         </is>
       </c>
     </row>
@@ -8114,22 +8198,22 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Bahrain Health Minister Participates in PHDC Global Conference</t>
+          <t>IAEA Initiative to Streamline Small Modular Reactor Deployment</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Manama</t>
+          <t>Vienna</t>
         </is>
       </c>
       <c r="F153" s="2" t="n">
@@ -8143,7 +8227,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -8153,7 +8237,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>https://www.bna.bh/en/HealthMinisterparticipatesinPHDCGlobalConference.aspx?cms=q8FmFJgiscL2fwIzON1%2BDnw8CXsPMB0KW78z%2FqJE8w8%3D</t>
+          <t>https://www.iaea.org/newscenter/news/iaea-initiative-to-streamline-smr-deployment-moving-to-implementation-phase</t>
         </is>
       </c>
     </row>
@@ -8165,26 +8249,26 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Putin Erdogan to Discuss Nuclear Power Plants and Gas Hub on Sidelines of BRICS Summit</t>
+          <t>PureHealth Launches Technology Platform to Enhance Access to Remote Healthcare Services</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Moscow</t>
+          <t>Abu Dhabi</t>
         </is>
       </c>
       <c r="F154" s="2" t="n">
-        <v>45588</v>
+        <v>45566</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -8194,7 +8278,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -8204,7 +8288,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>https://english.alarabiya.net/News/world/2024/10/23/putin-erdogan-to-discuss-nuclear-power-plants-gas-hub-on-sidelines-of-brics-</t>
+          <t>https://www.mediaoffice.abudhabi/en/health/purehealth-launches-technology-platform-to-enhance-access-to-remote-healthcare-services/</t>
         </is>
       </c>
     </row>
@@ -8221,21 +8305,21 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Reactor Assembly Completed for Bangladesh’s First Nuclear Plant</t>
+          <t>Vietnam proposes sole state investment in nuclear</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Dhaka</t>
+          <t>Hanoi</t>
         </is>
       </c>
       <c r="F155" s="2" t="n">
-        <v>45566</v>
+        <v>45589</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -8255,7 +8339,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>https://www.world-nuclear-news.org/articles/reactor-assembly-completed-for-bangladeshs-first-nuclear-plant</t>
+          <t>https://www.neimagazine.com/news/vietnam-proposes-sole-state-investment-in-nuclear/</t>
         </is>
       </c>
     </row>
@@ -8272,21 +8356,21 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>India Launches Fourth Nuclear Submarine into Water</t>
+          <t>Ontario needs more nuclear power to tackle demand</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>India</t>
+          <t xml:space="preserve">Canada </t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F156" s="2" t="n">
-        <v>45566</v>
+        <v>45588</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -8306,14 +8390,14 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/indias-fourth-nuclear-submarine-launched-into-water/article68783731.ece</t>
+          <t>https://www.thestar.com/politics/provincial/ford-government-says-ontario-needs-more-nuclear-power-to-tackle-rising-demand/article_5549a7b4-9169-11ef-8c0f-073525b0bd93.html</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -8323,21 +8407,21 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Latvia Improves Nuclear Safety Infrastructure</t>
+          <t>IAEA reports ongoing threats at Zaporizhia</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Zaporizhia</t>
         </is>
       </c>
       <c r="F157" s="2" t="n">
-        <v>45566</v>
+        <v>45588</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -8357,7 +8441,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>https://www.neimagazine.com/news/latvia-improves-nuclear-safety-infrastructure/</t>
+          <t>https://www.neimagazine.com/news/iaea-reports-ongoing-threats-at-zaporizhia/</t>
         </is>
       </c>
     </row>
@@ -8374,21 +8458,21 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Qatar Reaffirms Commitment to Nuclear Non Proliferation</t>
+          <t>Namibia to unlock development potential in nuclear</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Doha</t>
+          <t>Windhoek</t>
         </is>
       </c>
       <c r="F158" s="2" t="n">
-        <v>45566</v>
+        <v>45587</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -8398,7 +8482,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -8408,7 +8492,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>https://www.gulf-times.com/article/693061/qatar/qatar-reaffirms-commitment-to-continuing-efforts-toward-elimination-of-nuclear-weapons-and-nuclear-non-proliferation</t>
+          <t>https://www.observer24.com.na/nuclear-science-and-technology-conference-aims-to-unlock-development-potential/</t>
         </is>
       </c>
     </row>
@@ -8425,21 +8509,21 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>UK Nuclear Transport Ship to Test Rigid Sail Technology</t>
+          <t>Iran's nuclear strategy amidst regional conflict</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F159" s="2" t="n">
-        <v>45566</v>
+        <v>45589</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -8449,7 +8533,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -8459,7 +8543,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>https://maritime-executive.com/article/nuclear-transport-ship-to-test-uk-s-first-rigid-sail</t>
+          <t>https://foreignpolicy.com/2024/10/24/iran-nuclear-israel-strategy-weapons-missiles-hamas-hezbollah-axis-resistance/</t>
         </is>
       </c>
     </row>
@@ -8471,26 +8555,26 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>CBRNE Training Conference Focuses on Organizational and Clinical Aspects</t>
+          <t>Manila calls for global nuclear testing monitoring</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Manila</t>
         </is>
       </c>
       <c r="F160" s="2" t="n">
-        <v>45566</v>
+        <v>45588</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -8510,14 +8594,14 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>https://web.uniroma2.it/it/contenuto/eventi-cbrne-aspetti-organizzativi-e-clinici-il-convegno-per-la-formazione</t>
+          <t>https://www.bworldonline.com/the-nation/2024/10/23/630309/manila-bats-for-cooperation-in-global-nuclear-testing-monitoring-system/</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -8527,21 +8611,21 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Iran Submits Protest Note to IAEA Over Israeli Threats to Nuclear Sites</t>
+          <t>Nuclear energy hearing program launches</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Washington DC</t>
         </is>
       </c>
       <c r="F161" s="2" t="n">
-        <v>45566</v>
+        <v>45587</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -8551,7 +8635,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -8561,7 +8645,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>https://www.aa.com.tr/en/energy/nuclear/iran-submits-protest-note-to-iaea-over-israeli-threats-to-nuclear-sites/44088?amp=1</t>
+          <t>https://www.miragenews.com/nuclear-energy-hearing-program-launches-in-1343078/</t>
         </is>
       </c>
     </row>
@@ -8573,26 +8657,26 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>SDAIA and Saudi Health Ministry Agree to Manage National Health Data</t>
+          <t>Jamaica signs MoU with Canadian firms on nuclear energy</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Riyadh</t>
+          <t>Kingston</t>
         </is>
       </c>
       <c r="F162" s="2" t="n">
-        <v>45566</v>
+        <v>45589</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -8602,7 +8686,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -8612,7 +8696,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>https://www.zawya.com/en/business/healthcare/sdaia-and-health-ministry-agree-to-cooperate-in-managing-national-data-in-saudi-health-sector-p7a9n4fv</t>
+          <t>https://jamaica-gleaner.com/article/news/20241024/jamaica-signs-mou-canadian-firms-nuclear-energy</t>
         </is>
       </c>
     </row>
@@ -8624,26 +8708,26 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Azerbaijan's Nuclear Project Supports Regional Energy Integration</t>
+          <t>Bioelectronic device offers hope against bacterial infections</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Baku</t>
+          <t>Washington DC</t>
         </is>
       </c>
       <c r="F163" s="2" t="n">
-        <v>45566</v>
+        <v>45589</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -8653,7 +8737,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -8663,38 +8747,38 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>https://en.trend.az/business/3960432.html</t>
+          <t>https://today.ucsd.edu/story/innovative-bioelectronic-device-offers-new-hope-in-the-fight-against-bacterial-infections</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>IAEA Initiative to Streamline Small Modular Reactor Deployment</t>
+          <t>Bird flu outbreak in US, 31 human infections</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Vienna</t>
+          <t>Washington DC</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>45566</v>
+        <v>45588</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -8704,7 +8788,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -8714,7 +8798,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/news/iaea-initiative-to-streamline-smr-deployment-moving-to-implementation-phase</t>
+          <t>https://www.thehealthsite.com/news/bird-flu-outbreak-in-us-total-tally-of-human-infections-rises-to-31-in-the-country-1142080/</t>
         </is>
       </c>
     </row>
@@ -8726,22 +8810,22 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>PureHealth Launches Technology Platform to Enhance Access to Remote Healthcare Services</t>
+          <t>IAEA Completes International Physical Protection Advisory Service Mission in Congo</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Republic of Congo</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Brazzaville</t>
         </is>
       </c>
       <c r="F165" s="2" t="n">
@@ -8755,7 +8839,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -8765,7 +8849,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>https://www.mediaoffice.abudhabi/en/health/purehealth-launches-technology-platform-to-enhance-access-to-remote-healthcare-services/</t>
+          <t>https://www.iaea.org/newscenter/pressreleases/iaea-completes-international-physical-protection-advisory-service-mission-in-the-republic-of-the-congo</t>
         </is>
       </c>
     </row>
@@ -8782,21 +8866,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Vietnam proposes sole state investment in nuclear</t>
+          <t xml:space="preserve">Israel appears to avoid striking Iran's nuclear sites amid escalation warnings 
+</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Hanoi</t>
+          <t>Jerusalem</t>
         </is>
       </c>
       <c r="F166" s="2" t="n">
-        <v>45589</v>
+        <v>45590</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -8806,7 +8891,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -8816,38 +8901,38 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>https://www.neimagazine.com/news/vietnam-proposes-sole-state-investment-in-nuclear/</t>
+          <t>https://www.nbcnews.com/news/amp-video/mmvo222743109617</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Explosive</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Ontario needs more nuclear power to tackle demand</t>
+          <t>Explosions heard near Tehran</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Canada </t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F167" s="2" t="n">
-        <v>45588</v>
+        <v>45589</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -8857,7 +8942,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -8867,7 +8952,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>https://www.thestar.com/politics/provincial/ford-government-says-ontario-needs-more-nuclear-power-to-tackle-rising-demand/article_5549a7b4-9169-11ef-8c0f-073525b0bd93.html</t>
+          <t>https://www.timesofisrael.com/liveblog_entry/at-least-5-explosions-reportedly-heard-near-tehran/</t>
         </is>
       </c>
     </row>
@@ -8884,7 +8969,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>IAEA reports ongoing threats at Zaporizhia</t>
+          <t>IAEA updates on Ukraine nuclear situation</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8894,7 +8979,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Zaporizhia</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="F168" s="2" t="n">
@@ -8918,7 +9003,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>https://www.neimagazine.com/news/iaea-reports-ongoing-threats-at-zaporizhia/</t>
+          <t>https://www.iaea.org/newscenter/pressreleases/update-256-iaea-director-general-statement-on-situation-in-ukraine</t>
         </is>
       </c>
     </row>
@@ -8930,20 +9015,24 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Global race for advanced nuclear tech</t>
+          <t>Pakistan says next two weeks ‘critical’ for dengue infections amid surge in cases</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr"/>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Islamabad</t>
+        </is>
+      </c>
       <c r="F169" s="2" t="n">
         <v>45588</v>
       </c>
@@ -8955,7 +9044,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -8965,7 +9054,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>https://www.catf.us/resource/global-race-advanced-nuclear/</t>
+          <t>https://www.arabnews.pk/node/2576517/pakistan</t>
         </is>
       </c>
     </row>
@@ -8982,21 +9071,21 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Namibia to unlock development potential in nuclear</t>
+          <t>Russia Promotes Nuclear Plant for Proposed New Mongolian City</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Windhoek</t>
+          <t>Moscow</t>
         </is>
       </c>
       <c r="F170" s="2" t="n">
-        <v>45587</v>
+        <v>45566</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -9016,14 +9105,14 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>https://www.observer24.com.na/nuclear-science-and-technology-conference-aims-to-unlock-development-potential/</t>
+          <t>https://www.globalconstructionreview.com/russia-promotes-nuclear-plant-for-proposed-new-mongolian-city/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -9033,17 +9122,21 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>DIA releases nuclear challenges intelligence overview</t>
+          <t>Russia Promotes Nuclear Plant for Proposed New Mongolian City</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr"/>
+          <t>Mongolia</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Ulaanbatar</t>
+        </is>
+      </c>
       <c r="F171" s="2" t="n">
-        <v>45587</v>
+        <v>45566</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -9053,7 +9146,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -9063,34 +9156,34 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>https://www.dia.mil/News-Features/Articles/Article-View/Article/3943315/dia-releases-nuclear-challenges-intelligence-overview/</t>
+          <t>https://www.globalconstructionreview.com/russia-promotes-nuclear-plant-for-proposed-new-mongolian-city/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Iran's nuclear strategy amidst regional conflict</t>
+          <t>Rwanda confirms no Marburg virus community transmission</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Kigali</t>
         </is>
       </c>
       <c r="F172" s="2" t="n">
@@ -9114,7 +9207,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>https://foreignpolicy.com/2024/10/24/iran-nuclear-israel-strategy-weapons-missiles-hamas-hezbollah-axis-resistance/</t>
+          <t>https://www.myjoyonline.com/rwanda-says-no-community-transmission-of-marburg-virus-with-zero-new-infections-in-recent-days/</t>
         </is>
       </c>
     </row>
@@ -9131,21 +9224,21 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Manila calls for global nuclear testing monitoring</t>
+          <t>Sky Soldiers conduct CBRN training</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Manila</t>
+          <t>Washington DC</t>
         </is>
       </c>
       <c r="F173" s="2" t="n">
-        <v>45588</v>
+        <v>45589</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -9165,7 +9258,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>https://www.bworldonline.com/the-nation/2024/10/23/630309/manila-bats-for-cooperation-in-global-nuclear-testing-monitoring-system/</t>
+          <t>https://www.dvidshub.net/video/941147/b-roll-package-sky-soldiers-conduct-cbrn-training-during-e3b</t>
         </is>
       </c>
     </row>
@@ -9182,21 +9275,21 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Nuclear energy hearing program launches</t>
+          <t>UAE to take nuclear plant next step</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>Abu Dhabi</t>
         </is>
       </c>
       <c r="F174" s="2" t="n">
-        <v>45587</v>
+        <v>45589</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -9216,7 +9309,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>https://www.miragenews.com/nuclear-energy-hearing-program-launches-in-1343078/</t>
+          <t>https://www.meed.com/uae-to-take-nuclear-plant-next-step</t>
         </is>
       </c>
     </row>
@@ -9233,17 +9326,17 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Jamaica signs MoU with Canadian firms on nuclear energy</t>
+          <t>Mochovce 4 passes safety system tests</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Kingston</t>
+          <t>Mochovce</t>
         </is>
       </c>
       <c r="F175" s="2" t="n">
@@ -9257,7 +9350,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -9267,38 +9360,38 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>https://jamaica-gleaner.com/article/news/20241024/jamaica-signs-mou-canadian-firms-nuclear-energy</t>
+          <t>https://www.world-nuclear-news.org/articles/mochovce-4-passes-safety-system-tests</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Bioelectronic device offers hope against bacterial infections</t>
+          <t>250 cases of Russia using chemical weapons in Ukraine recorded in September</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>Moscow</t>
         </is>
       </c>
       <c r="F176" s="2" t="n">
-        <v>45589</v>
+        <v>45565</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -9318,7 +9411,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>https://today.ucsd.edu/story/innovative-bioelectronic-device-offers-new-hope-in-the-fight-against-bacterial-infections</t>
+          <t>https://bukvy.org/en/250-cases-of-russia-using-chemical-weapons-in-ukraine-recorded-in-september/</t>
         </is>
       </c>
     </row>
@@ -9330,26 +9423,26 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bird flu outbreak in US, 31 human infections</t>
+          <t>250 cases of Russia using chemical weapons in Ukraine recorded in September</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="F177" s="2" t="n">
-        <v>45588</v>
+        <v>45565</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -9369,7 +9462,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>https://www.thehealthsite.com/news/bird-flu-outbreak-in-us-total-tally-of-human-infections-rises-to-31-in-the-country-1142080/</t>
+          <t>https://bukvy.org/en/250-cases-of-russia-using-chemical-weapons-in-ukraine-recorded-in-september/</t>
         </is>
       </c>
     </row>
@@ -9386,21 +9479,21 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>IAEA Completes International Physical Protection Advisory Service Mission in Congo</t>
+          <t>China expanding nuclear arsenal rapidly, Pentagon says</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Republic of Congo</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Brazzaville</t>
+          <t>Beijing</t>
         </is>
       </c>
       <c r="F178" s="2" t="n">
-        <v>45566</v>
+        <v>45589</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -9410,7 +9503,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -9420,7 +9513,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/pressreleases/iaea-completes-international-physical-protection-advisory-service-mission-in-the-republic-of-the-congo</t>
+          <t>https://www.defensenews.com/pentagon/2024/10/24/china-leading-rapid-expansion-of-nuclear-arsenal-pentagon-says/</t>
         </is>
       </c>
     </row>
@@ -9437,22 +9530,21 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Israel appears to avoid striking Iran's nuclear sites amid escalation warnings 
-</t>
+          <t>Azerbaijan expands nuclear energy capacity</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Jerusalem</t>
+          <t>Baku</t>
         </is>
       </c>
       <c r="F179" s="2" t="n">
-        <v>45590</v>
+        <v>45589</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -9462,7 +9554,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -9472,38 +9564,38 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>https://www.nbcnews.com/news/amp-video/mmvo222743109617</t>
+          <t>https://en.trend.az/business/3961814.html</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Explosions heard near Tehran</t>
+          <t>Senegal to Establish Nuclear Reactors for Training and Research</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Dakar</t>
         </is>
       </c>
       <c r="F180" s="2" t="n">
-        <v>45589</v>
+        <v>45566</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -9513,7 +9605,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -9523,7 +9615,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>https://www.timesofisrael.com/liveblog_entry/at-least-5-explosions-reportedly-heard-near-tehran/</t>
+          <t>https://energycapitalpower.com/senegal-to-establish-nuclear-reactors-for-training-research/</t>
         </is>
       </c>
     </row>
@@ -9535,22 +9627,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Explosion proof laptop for hazardous environments unveiled</t>
+          <t>Ajman Chamber Participates in 16th Arab German Health Summit</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr"/>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Ajman</t>
+        </is>
+      </c>
       <c r="F181" s="2" t="n">
-        <v>45588</v>
+        <v>45566</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -9560,7 +9656,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -9570,14 +9666,14 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>https://www.hazardexonthenet.net/article/210054/COBIC-Ex-unveils-F112-LT-Ex--Explosion-proof-laptop-for-hazardous-environments.aspx</t>
+          <t>https://www.wam.ae/en/article/b5uex8n-ajman-chamber-participates-16th-arab-german-health</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -9587,21 +9683,21 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>IAEA updates on Ukraine nuclear situation</t>
+          <t>Slovenia Calls Off Nuclear Referendum</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Ljubljana</t>
         </is>
       </c>
       <c r="F182" s="2" t="n">
-        <v>45588</v>
+        <v>45566</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -9611,7 +9707,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -9621,7 +9717,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/pressreleases/update-256-iaea-director-general-statement-on-situation-in-ukraine</t>
+          <t>https://www.neimagazine.com/news/slovenia-calls-off-nuclear-referendum/</t>
         </is>
       </c>
     </row>
@@ -9633,22 +9729,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>AI helps manage nuclear waste, AI and tech firms in focus</t>
+          <t>DOH and Accenture Collaborate to Drive Digital Transformation in Healthcare</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr"/>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
       <c r="F183" s="2" t="n">
-        <v>45589</v>
+        <v>45566</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -9658,7 +9758,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -9668,7 +9768,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>https://www.barrons.com/articles/google-amazon-ai-nuclear-waste-16fb39ab</t>
+          <t>https://www.wam.ae/en/article/b5uexhe-doh-accenture-collaborate-drive-digital</t>
         </is>
       </c>
     </row>
@@ -9685,17 +9785,17 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Pakistan says next two weeks ‘critical’ for dengue infections amid surge in cases</t>
+          <t>Singapore, Thailand implement health screenings for mpox</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Islamabad</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F184" s="2" t="n">
@@ -9719,7 +9819,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>https://www.arabnews.pk/node/2576517/pakistan</t>
+          <t>https://www.travelandtourworld.com/news/article/singapore-thailand-implement-health-screenings-amid-rise-in-mpox-infections/</t>
         </is>
       </c>
     </row>
@@ -9731,26 +9831,26 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Russia Promotes Nuclear Plant for Proposed New Mongolian City</t>
+          <t>Singapore, Thailand implement health screenings for mpox</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Russia, Mongolia</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Moscow, Ulaanbatar</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="F185" s="2" t="n">
-        <v>45566</v>
+        <v>45588</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -9760,7 +9860,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -9770,38 +9870,38 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>https://www.globalconstructionreview.com/russia-promotes-nuclear-plant-for-proposed-new-mongolian-city/</t>
+          <t>https://www.travelandtourworld.com/news/article/singapore-thailand-implement-health-screenings-amid-rise-in-mpox-infections/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Rwanda confirms no Marburg virus community transmission</t>
+          <t>Japan Renews Focus on Nuclear Energy Post0Fukushima</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Kigali</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F186" s="2" t="n">
-        <v>45589</v>
+        <v>45566</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -9811,7 +9911,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -9821,7 +9921,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>https://www.myjoyonline.com/rwanda-says-no-community-transmission-of-marburg-virus-with-zero-new-infections-in-recent-days/</t>
+          <t>https://www.ucanews.com/news/japan-renews-focus-on-nuclear-energy-post-fukushima/106776</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9938,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Sky Soldiers conduct CBRN training</t>
+          <t>DIA Report on Nuclear Threats from China, Russia, Iran, North Korea</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -9852,7 +9952,7 @@
         </is>
       </c>
       <c r="F187" s="2" t="n">
-        <v>45589</v>
+        <v>45566</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -9862,7 +9962,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -9872,38 +9972,38 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>https://www.dvidshub.net/video/941147/b-roll-package-sky-soldiers-conduct-cbrn-training-during-e3b</t>
+          <t>https://executivegov.com/2024/10/dia-nuclear-threat-report-china-russia-iran-north-korea/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>UAE to take nuclear plant next step</t>
+          <t>Cholera death toll rises amid crisis in South Sudan</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>South Sudan</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Juba</t>
         </is>
       </c>
       <c r="F188" s="2" t="n">
-        <v>45589</v>
+        <v>45566</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -9913,7 +10013,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -9923,7 +10023,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>https://www.meed.com/uae-to-take-nuclear-plant-next-step</t>
+          <t>https://bulawayo24.com/index-id-news-sc-national-byo-246963.html</t>
         </is>
       </c>
     </row>
@@ -9940,17 +10040,21 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Modelling nuclear energy’s economic contribution</t>
+          <t>Romania to Contract New Nuclear Reactors</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr"/>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
       <c r="F189" s="2" t="n">
-        <v>45589</v>
+        <v>45566</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -9970,7 +10074,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/publications/15295/modelling-the-contribution-of-nuclear-energy-to-economic-development</t>
+          <t>https://www.romania-insider.com/contract-new-nuclear-reactors-romania-october-2024</t>
         </is>
       </c>
     </row>
@@ -9987,21 +10091,21 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Mochovce 4 passes safety system tests</t>
+          <t>TEPCO Conducts Trial for Debris Removal at Fukushima Nuclear Plant</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Mochovce</t>
+          <t>Fukushima</t>
         </is>
       </c>
       <c r="F190" s="2" t="n">
-        <v>45589</v>
+        <v>45566</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -10011,7 +10115,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -10021,7 +10125,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>https://www.world-nuclear-news.org/articles/mochovce-4-passes-safety-system-tests</t>
+          <t>https://www.japantimes.co.jp/news/2024/10/28/japan/tepco-debris-removal-trial/</t>
         </is>
       </c>
     </row>
@@ -10038,21 +10142,21 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>250 cases of Russia using chemical weapons in Ukraine recorded in September</t>
+          <t>Spanish Police Intercept 13 Tonnes of Chemical Weapons Precursors Bound for Russia</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Russia, Ukraine</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Moscow, Kyiv</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="F191" s="2" t="n">
-        <v>45565</v>
+        <v>45581</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -10062,7 +10166,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -10072,38 +10176,38 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>https://bukvy.org/en/250-cases-of-russia-using-chemical-weapons-in-ukraine-recorded-in-september/</t>
+          <t>https://www.euronews.com/2024/10/16/spanish-police-intercept-13-tonnes-of-chemical-weapons-precursors-bound-for-russia</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Explosive</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>China expanding nuclear arsenal rapidly, Pentagon says</t>
+          <t>Russia Ukraine Drone Attack Sets Fire to Oil Facility</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>kyiv</t>
         </is>
       </c>
       <c r="F192" s="2" t="n">
-        <v>45589</v>
+        <v>45566</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -10113,7 +10217,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -10123,7 +10227,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>https://www.defensenews.com/pentagon/2024/10/24/china-leading-rapid-expansion-of-nuclear-arsenal-pentagon-says/</t>
+          <t>https://www.newsweek.com/russia-ukraine-drones-oil-fire-1968024</t>
         </is>
       </c>
     </row>
@@ -10135,26 +10239,26 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Azerbaijan expands nuclear energy capacity</t>
+          <t>Russian Ship to Unload 20,000 Tons of Dangerous Cargo at Great Yarmouth Port</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Baku</t>
+          <t>Great Yarmouth</t>
         </is>
       </c>
       <c r="F193" s="2" t="n">
-        <v>45589</v>
+        <v>45566</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -10164,7 +10268,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environmental</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -10174,7 +10278,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>https://en.trend.az/business/3961814.html</t>
+          <t>https://www.marineinsight.com/shipping-news/russian-ship-to-unload-20000-tons-of-dangerous-cargo-at-great-yarmouth-port/</t>
         </is>
       </c>
     </row>
@@ -10191,21 +10295,21 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Senegal to Establish Nuclear Reactors for Training and Research</t>
+          <t>Putin Orders Strategic Nuclear Training Exercise</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Dakar</t>
+          <t>Moscow</t>
         </is>
       </c>
       <c r="F194" s="2" t="n">
-        <v>45566</v>
+        <v>45594</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -10225,7 +10329,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>https://energycapitalpower.com/senegal-to-establish-nuclear-reactors-for-training-research/</t>
+          <t>https://english.alarabiya.net/News/world/2024/10/29/putin-orders-strategic-nuclear-training-exercise</t>
         </is>
       </c>
     </row>
@@ -10237,26 +10341,26 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Ajman Chamber Participates in 16th Arab German Health Summit</t>
+          <t>Meet America's Secret Team of Nuclear First Responders</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Washington DC</t>
         </is>
       </c>
       <c r="F195" s="2" t="n">
-        <v>45566</v>
+        <v>45594</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -10276,38 +10380,38 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>https://www.wam.ae/en/article/b5uex8n-ajman-chamber-participates-16th-arab-german-health</t>
+          <t>https://www.wkyufm.org/news/2024-10-29/meet-americas-secret-team-of-nuclear-first-responders</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Slovenia Calls Off Nuclear Referendum</t>
+          <t>Zimbabwe Reports First Two Mpox Cases, Unspecified Variant</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Ljubljana</t>
+          <t>Harare</t>
         </is>
       </c>
       <c r="F196" s="2" t="n">
-        <v>45566</v>
+        <v>45578</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -10317,7 +10421,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -10327,7 +10431,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>https://www.neimagazine.com/news/slovenia-calls-off-nuclear-referendum/</t>
+          <t>https://www.reuters.com/world/africa/zimbabwe-reports-first-two-mpox-cases-unspecified-variant-2024-10-13/</t>
         </is>
       </c>
     </row>
@@ -10339,22 +10443,26 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Global Action Plan for Health Through Biodiversity</t>
+          <t>Japan Plans to Restart Nuclear Reactors Post Fukushima</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr"/>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
       <c r="F197" s="2" t="n">
-        <v>45566</v>
+        <v>45594</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -10364,7 +10472,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -10374,7 +10482,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>https://www.unep.org/news-and-stories/speech/global-action-plan-health-through-biodiversity</t>
+          <t>https://www3.nhk.or.jp/nhkworld/en/news/20241029_26/</t>
         </is>
       </c>
     </row>
@@ -10386,26 +10494,26 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>DOH and Accenture Collaborate to Drive Digital Transformation in Healthcare</t>
+          <t>Full Scale Nuclear Emergency Exercise Set for Oct 29030</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Saint John</t>
         </is>
       </c>
       <c r="F198" s="2" t="n">
-        <v>45566</v>
+        <v>45594</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -10425,7 +10533,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>https://www.wam.ae/en/article/b5uexhe-doh-accenture-collaborate-drive-digital</t>
+          <t>https://saintjohn.ca/en/news-and-notices/full-scale-nuclear-emergency-exercise-set-october-29-and-30</t>
         </is>
       </c>
     </row>
@@ -10437,26 +10545,26 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Singapore, Thailand implement health screenings for mpox</t>
+          <t>Nuclear Energy Roundtable in USA</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Singapore, Thailand</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Singapore, Bangkok</t>
+          <t>Washington DC</t>
         </is>
       </c>
       <c r="F199" s="2" t="n">
-        <v>45588</v>
+        <v>45566</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -10466,7 +10574,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -10476,7 +10584,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>https://www.travelandtourworld.com/news/article/singapore-thailand-implement-health-screenings-amid-rise-in-mpox-infections/</t>
+          <t>https://www.wxow.com/news/van-orden-attends-nuclear-energy-roundtable/article_031ee7f8-9572-11ef-a320-03dcf6932c77.html</t>
         </is>
       </c>
     </row>
@@ -10493,17 +10601,17 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Japan Renews Focus on Nuclear Energy Post0Fukushima</t>
+          <t>Independent Review Assesses IAEA's Internal Safety Regulatory System</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F200" s="2" t="n">
@@ -10517,7 +10625,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -10527,38 +10635,38 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>https://www.ucanews.com/news/japan-renews-focus-on-nuclear-energy-post-fukushima/106776</t>
+          <t>https://www.iaea.org/newscenter/pressreleases/independent-review-assesses-iaeas-internal-safety-regulatory-system-for-first-time-finds-well-established-framework</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>DIA Report on Nuclear Threats from China, Russia, Iran, North Korea</t>
+          <t>COVID May Increase Risk of Death Years After Infection</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F201" s="2" t="n">
-        <v>45566</v>
+        <v>45574</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -10568,7 +10676,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -10578,34 +10686,34 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>https://executivegov.com/2024/10/dia-nuclear-threat-report-china-russia-iran-north-korea/</t>
+          <t>https://www.allsides.com/news/2024-10-09-1415/coronavirus-covid-may-increase-risk-death-years-after-infection-study</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Cholera death toll rises amid crisis in South Sudan</t>
+          <t>7th International Conference on CBRNE Research and Innovation, 2026</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>South Sudan</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Juba</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F202" s="2" t="n">
@@ -10629,7 +10737,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>https://bulawayo24.com/index-id-news-sc-national-byo-246963.html</t>
+          <t>https://ctif.org/events/7th-international-conference-cbrne-research-and-innovation-2026</t>
         </is>
       </c>
     </row>
@@ -10646,17 +10754,17 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Romania to Contract New Nuclear Reactors</t>
+          <t>Voters Back Nuclear Power Plant Construction in National Referendum</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Bucharest</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F203" s="2" t="n">
@@ -10680,7 +10788,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>https://www.romania-insider.com/contract-new-nuclear-reactors-romania-october-2024</t>
+          <t>https://www.nucnet.org/news/voters-back-nuclear-power-plant-construction-in-national-referendum-10-1-2024</t>
         </is>
       </c>
     </row>
@@ -10697,17 +10805,17 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>TEPCO Conducts Trial for Debris Removal at Fukushima Nuclear Plant</t>
+          <t>Industry Lays Groundwork for Reactor Deployment with First Comprehensive Set of Rules</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Fukushima</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F204" s="2" t="n">
@@ -10721,7 +10829,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -10731,38 +10839,38 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>https://www.japantimes.co.jp/news/2024/10/28/japan/tepco-debris-removal-trial/</t>
+          <t>https://www.nucnet.org/news/industry-lays-groundwork-for-reactor-deployment-with-first-comprehensive-set-of-rules-10-1-2024</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spanish Police Intercept 13 Tonnes of Chemical Weapons Precursors Bound for Russia</t>
+          <t>NucNet Launches Global Small Modular and Advanced Reactor Database</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F205" s="2" t="n">
-        <v>45581</v>
+        <v>45566</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -10782,34 +10890,34 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>https://www.euronews.com/2024/10/16/spanish-police-intercept-13-tonnes-of-chemical-weapons-precursors-bound-for-russia</t>
+          <t>https://www.nucnet.org/news/nucnet-launches-global-small-modular-and-advanced-reactor-database-10-4-2024</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Russia Ukraine Drone Attack Sets Fire to Oil Facility</t>
+          <t>Plasma Heating Prediction Made 10 Million Times Faster in Fusion Research</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>kyiv</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F206" s="2" t="n">
@@ -10823,7 +10931,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -10833,7 +10941,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>https://www.newsweek.com/russia-ukraine-drones-oil-fire-1968024</t>
+          <t>https://interestingengineering.com/Economic/plasma-heating-prediction-made-10-million-times-faster</t>
         </is>
       </c>
     </row>
@@ -10845,22 +10953,22 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Radiological</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Russian Ship to Unload 20,000 Tons of Dangerous Cargo at Great Yarmouth Port</t>
+          <t>The Role of IAEA in Nuclear and Radiological Emergency Response</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Great Yarmouth</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F207" s="2" t="n">
@@ -10874,7 +10982,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -10884,7 +10992,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>https://www.marineinsight.com/shipping-news/russian-ship-to-unload-20000-tons-of-dangerous-cargo-at-great-yarmouth-port/</t>
+          <t>https://www.iaea.org/newscenter/news/from-preparedness-to-resilience-the-role-of-the-iaea-in-nuclear-and-radiological-emergency-response</t>
         </is>
       </c>
     </row>
@@ -10896,26 +11004,26 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Putin Orders Strategic Nuclear Training Exercise</t>
+          <t>AI Discovers Over 160,000 New RNA Viruses</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Moscow</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F208" s="2" t="n">
-        <v>45594</v>
+        <v>45566</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -10925,7 +11033,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -10935,7 +11043,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>https://english.alarabiya.net/News/world/2024/10/29/putin-orders-strategic-nuclear-training-exercise</t>
+          <t>https://scitechdaily.com/revolutionizing-virology-ai-discovers-over-160000-new-rna-viruses/</t>
         </is>
       </c>
     </row>
@@ -10947,12 +11055,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>WHO High Level Meeting on One Health</t>
+          <t>Study Finds Evidence of Chemical Leak at Major Facility</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -10960,9 +11068,13 @@
           <t>International</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="F209" s="2" t="n">
-        <v>45595</v>
+        <v>45581</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -10972,7 +11084,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Environmental</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -10982,7 +11094,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>https://www.who.int/news-room/events/detail/2024/10/30/default-calendar/g20-high-level-meeting-on-one-health</t>
+          <t>https://redirect.viglink.com?u=https%3A%2F%2Fwww.nature.com%2Farticles%2Fs41467-024-53085-9&amp;key=a7e37b5f6ff1de9cb410158b1013e54a&amp;prodOvrd=RAC&amp;opt=false</t>
         </is>
       </c>
     </row>
@@ -10999,21 +11111,21 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Meet America's Secret Team of Nuclear First Responders</t>
+          <t>Uranium Enrichment Milestones: Urenco Centrifuge Developments</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F210" s="2" t="n">
-        <v>45594</v>
+        <v>45566</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -11023,7 +11135,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -11033,14 +11145,14 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>https://www.wkyufm.org/news/2024-10-29/meet-americas-secret-team-of-nuclear-first-responders</t>
+          <t>https://interestingengineering.com/Economic/uranium-enrichment-urenco-centrifuge-milestones</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -11050,21 +11162,21 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Zimbabwe Reports First Two Mpox Cases, Unspecified Variant</t>
+          <t>WHO Warns of Rising Pandemic Threats</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Harare</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F211" s="2" t="n">
-        <v>45578</v>
+        <v>45566</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -11084,7 +11196,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/africa/zimbabwe-reports-first-two-mpox-cases-unspecified-variant-2024-10-13/</t>
+          <t>https://www.wam.ae/en/article/b5ogl9j-new-risks-raise-pandemic-threat-global-scale-who</t>
         </is>
       </c>
     </row>
@@ -11101,21 +11213,21 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Japan Plans to Restart Nuclear Reactors Post Fukushima</t>
+          <t>Google Signs Deal to Buy Power from SMRs for Data Centres</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F212" s="2" t="n">
-        <v>45594</v>
+        <v>45566</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -11135,7 +11247,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>https://www3.nhk.or.jp/nhkworld/en/news/20241029_26/</t>
+          <t>https://www.nucnet.org/news/google-signs-world-first-deal-to-buy-power-from-small-modular-reactors-for-data-centres-10-2-2024</t>
         </is>
       </c>
     </row>
@@ -11147,12 +11259,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>WHO Activates Global Health Emergency Corps for Mpox Outbreak</t>
+          <t>IAEA Annual Report Presented to UN General Assembly</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -11160,9 +11272,13 @@
           <t>International</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="F213" s="2" t="n">
-        <v>45594</v>
+        <v>45205</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -11172,7 +11288,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -11182,7 +11298,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>https://www.who.int/news/item/29-10-2024-who-and-partners-activate-global-health-emergency-corps-for-the-first-time-in-response-to-mpox-outbreak</t>
+          <t>https://www.iaea.org/newscenter/news/2023-iaea-annual-report-presented-to-the-un-general-assembly</t>
         </is>
       </c>
     </row>
@@ -11194,26 +11310,26 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Full Scale Nuclear Emergency Exercise Set for Oct 29030</t>
+          <t>WHO Releases Pandemic Preparedness Guidelines</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Saint John</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F214" s="2" t="n">
-        <v>45594</v>
+        <v>45566</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -11233,7 +11349,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>https://saintjohn.ca/en/news-and-notices/full-scale-nuclear-emergency-exercise-set-october-29-and-30</t>
+          <t>https://www.who.int/publications/i/item/9789240101456</t>
         </is>
       </c>
     </row>
@@ -11250,41 +11366,704 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Nuclear Energy Roundtable in USA</t>
+          <t>Agency plans next workshops in bid to advance nuclear in Europe and Eurasia</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Washington DC</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F215" s="2" t="n">
+        <v>45392</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>https://www.nucnet.org/news/agency-plans-next-workshops-in-bid-to-advance-nuclear-inn-europe-and-eurasia-10-4-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Alliance calls for commission to fully recognize nuclear in paradigm policy shift</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="n">
+        <v>45392</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>https://www.nucnet.org/news/alliance-calls-for-commission-to-fully-recognise-nuclear-in-paradigm-policy-shift-10-4-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Biological</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>WHO Publication on health information (disease data)</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="n">
+        <v>45392</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0</v>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>https://www.who.int/publications/i/item/9789240098619</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Small Modular Reactors Advances in SMR Developments</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>https://www.iaea.org/publications/15790/small-modular-reactors-advances-in-smr-developments-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Radiological, Nuclear</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>New Coordinated Research Project CRP optimizing mining wastewater remediation</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="n">
+        <v>45582</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>https://www.iaea.org/newscenter/news/new-coordinated-research-project-crp-optimizing-mining-wastewater-remediation</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Investment in nuclear must rapidly increase to USD125 billion a year</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="n">
+        <v>45301</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>https://www.nucnet.org/news/investment-in-nuclear-must-rapidly-increase-to-usd125-billion-a-year-10-1-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Global race for advanced nuclear tech</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="n">
+        <v>45588</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0</v>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>https://www.catf.us/resource/global-race-advanced-nuclear/</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Incident</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>DIA releases nuclear challenges intelligence overview</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="n">
+        <v>45587</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0</v>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>https://www.dia.mil/News-Features/Articles/Article-View/Article/3943315/dia-releases-nuclear-challenges-intelligence-overview/</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Explosive</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Explosion proof laptop for hazardous environments unveiled</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="n">
+        <v>45588</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0</v>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>https://www.hazardexonthenet.net/article/210054/COBIC-Ex-unveils-F112-LT-Ex--Explosion-proof-laptop-for-hazardous-environments.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>AI helps manage nuclear waste, AI and tech firms in focus</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="n">
+        <v>45589</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>https://www.barrons.com/articles/google-amazon-ai-nuclear-waste-16fb39ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Nuclear</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Modelling nuclear energy’s economic contribution</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="n">
+        <v>45589</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>https://www.iaea.org/publications/15295/modelling-the-contribution-of-nuclear-energy-to-economic-development</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Biological</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Global Action Plan for Health Through Biodiversity</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="G215" t="n">
-        <v>0</v>
-      </c>
-      <c r="H215" t="n">
-        <v>0</v>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>Economic</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>https://www.wxow.com/news/van-orden-attends-nuclear-energy-roundtable/article_031ee7f8-9572-11ef-a320-03dcf6932c77.html</t>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0</v>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>https://www.unep.org/news-and-stories/speech/global-action-plan-health-through-biodiversity</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Biological</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>WHO High Level Meeting on One Health</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="n">
+        <v>45595</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>https://www.who.int/news-room/events/detail/2024/10/30/default-calendar/g20-high-level-meeting-on-one-health</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Biological</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>WHO Activates Global Health Emergency Corps for Mpox Outbreak</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="n">
+        <v>45594</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>https://www.who.int/news/item/29-10-2024-who-and-partners-activate-global-health-emergency-corps-for-the-first-time-in-response-to-mpox-outbreak</t>
         </is>
       </c>
     </row>

--- a/News GIS.xlsx
+++ b/News GIS.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K228"/>
+  <dimension ref="A1:L228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,6 +488,11 @@
           <t>Full Link</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Coordinates</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -539,6 +544,7 @@
           <t>https://www.cbsnews.com/sacramento/news/large-explosions-reported-near-sikh-temple-in-south-sacramento-area/</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -590,6 +596,7 @@
           <t>https://www.freemalaysiatoday.com/category/nation/2024/04/22/3-factory-workers-injured-in-kota-kemuning-nitrogen-gas-explosion/</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -641,6 +648,7 @@
           <t>https://www.ndtv.com/kerala-news/bird-flu-outbreak-reported-in-keralas-alappuzha-5466502</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -692,6 +700,7 @@
           <t>https://sputnikglobe.com/20240411/radiation-leak-detected-at-metallurgical-plant-in-eastern-france---reports-1117875818.html</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -743,6 +752,7 @@
           <t>https://www.insauga.com/worker-dies-after-chemical-exposure-at-burlington-warehouse/</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -794,6 +804,7 @@
           <t>https://ptvnews.ph/toxic-chemicals-found-in-lucky-charm-bracelets/#google_vignette</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -845,6 +856,7 @@
           <t>https://www.who.int/news/item/26-04-2024-who-and-france-convene-high-level-meeting-to-defeat-meningitis--paralympians-join-effort-to-tackle-deadly-disease</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -896,6 +908,7 @@
           <t>https://ktar.com/story/5571477/15-employees-hospitalized-after-hazmat-incident-at-west-valley-warehouse/</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -947,6 +960,7 @@
           <t>https://www.perthnow.com.au/news/weather/illness-linked-to-contaminated-water-after-uae-floods-c-14441524</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -998,6 +1012,7 @@
           <t>https://www.malaymail.com/news/world/2024/04/24/congo-republic-declares-mpox-epidemic/130549#google_vignette</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1049,6 +1064,7 @@
           <t>https://www.reuters.com/world/asia-pacific/unstable-nuclear-waste-dams-threaten-fertile-central-asia-heartland-2024-04-23/</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1100,6 +1116,7 @@
           <t>https://www.themoscowtimes.com/2024/04/22/russias-record-floods-submerge-uranium-mines-in-urals-reports-a84919</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1151,6 +1168,7 @@
           <t>https://www.msn.com/en-au/health/other/nasa-finds-mutant-bacteria-on-iss-that-doesn-t-exist-on-earth/ar-AA1nszZU</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1202,6 +1220,7 @@
           <t>https://www.bangkokpost.com/thailand/general/2780057/chemical-warehouse-explosions-prompt-evacuations</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1253,6 +1272,7 @@
           <t>https://sofiaglobe.com/2024/04/20/first-batch-of-westinghouse-manufactured-nuclear-fuel-delivered-to-bulgarias-kozloduy-power-station/</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1304,6 +1324,7 @@
           <t>https://www.powderbulksolids.com/industrial-fires-explosions/2-killed-in-chemical-plant-explosion</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1355,6 +1376,7 @@
           <t>https://abc11.com/gas-leak-30-000-pound-propane-tank/14689532/</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1406,6 +1428,7 @@
           <t>https://balkaninsight.com/2024/10/28/albania-prosecution-orders-seizure-of-suspected-hazardous-waste-on-ship/</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1457,6 +1480,7 @@
           <t>https://www.enerdata.net/publications/daily-energy-news/khnp-will-lead-study-start-bataan-nuclear-plant-philippines.html</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1508,6 +1532,7 @@
           <t>https://vp-mi.com/news/2024/oct/09/training-day-simulates-hazmat-accident/</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1559,6 +1584,7 @@
           <t>https://al24news.com/en/algeria-and-china-discuss-expanding-cooperation-in-nuclear-technologies/</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1610,6 +1636,7 @@
           <t>https://al24news.com/en/algeria-and-china-discuss-expanding-cooperation-in-nuclear-technologies/</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1661,6 +1688,7 @@
           <t>https://www.neimagazine.com/news/iaea-chief-holds-high-level-talks-in-belarus/</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1712,6 +1740,7 @@
           <t>https://energycentral.com/news/rooppur-npp-engineers-receive-training-nuclear-fuel-handling</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1763,6 +1792,7 @@
           <t>https://www.power-eng.com/nuclear/smrs/report-explores-use-cases-for-advanced-nuclear-energy/#gref</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1814,6 +1844,7 @@
           <t>https://www.iaea.org/newscenter/news/politecnico-di-milano-designated-as-iaea-collaborating-centre</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1865,6 +1896,7 @@
           <t>https://www.iaea.org/newscenter/news/iaea-director-general-in-slovenia-before-key-nuclear-power-referendum</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1916,6 +1948,7 @@
           <t>https://www.zawya.com/en/economy/africa/congo-launches-its-first-mpox-vaccination-campaign-mmywcnro</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1967,6 +2000,7 @@
           <t>https://www.bulktransporter.com/regulations/article/55234222/phmsa-proposes-changes-to-hazmat-transport-rule</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2018,6 +2052,7 @@
           <t>https://abc30.com/amp/post/possible-case-bird-flu-detected-central-valley/15397102/</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2069,6 +2104,7 @@
           <t>https://www.iaea.org/newscenter/pressreleases/update-254-iaea-director-general-statement-on-situation-in-ukraine</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2120,6 +2156,7 @@
           <t>https://theloadstar.com/china-tightens-rules-on-hazardous-cargo-at-ningbo/</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2171,6 +2208,7 @@
           <t>https://www.meed.com/execution-to-start-for-major-egypt-chemicals-project</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2222,6 +2260,7 @@
           <t>https://www.iaea.org/newscenter/pressreleases/iaea-concludes-long-term-operation-safety-review-at-swedens-oskarshamn-nuclear-power-plant</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2273,6 +2312,7 @@
           <t>https://www.pravda.com.ua/eng/news/2024/10/10/7479090/</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2324,6 +2364,7 @@
           <t>https://www.world-nuclear-news.org/articles/korea-czech-republic-team-up-on-hydrogen-production</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2375,6 +2416,7 @@
           <t>https://www.timesofisrael.com/iran-backed-houthis-attack-chemical-tanker-in-red-sea-no-injuries-or-fire-reported/</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2426,6 +2468,7 @@
           <t>https://www.timesofisrael.com/iran-backed-houthis-attack-chemical-tanker-in-red-sea-no-injuries-or-fire-reported/</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2477,6 +2520,7 @@
           <t>https://www.timesofisrael.com/iran-threatens-to-escalate-if-israel-attacks-says-nuclear-or-oil-targets-a-red-line/</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2528,6 +2572,7 @@
           <t>https://interestingengineering.com/energy/china-boron-10-enrichment-nuclear-energy</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2579,6 +2624,7 @@
           <t>https://www.news18.com/world/iran-hit-by-heavy-cyberattacks-targeting-its-nuclear-facilities-amid-middle-east-tensions-9083699.html</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2630,6 +2676,7 @@
           <t>https://www.world-nuclear-news.org/articles/Slovakia%20gets%20USD5%20million%20grant%20for%20SMR%20project</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2681,6 +2728,7 @@
           <t>https://www.world-nuclear-news.org/articles/First%20reactor%20launched%20for%20Yakutia%20nuclear%20icebreaker</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2732,6 +2780,7 @@
           <t>https://www.world-nuclear-news.org/articles/digital-twin-of-apr1400-control-systems-created</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2783,6 +2832,7 @@
           <t>https://interestingengineering.com/energy/nuclear-power-generator-for-deep-space-missions</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2834,6 +2884,7 @@
           <t>https://www.world-nuclear-news.org/articles/us-startup-aims-for-shipyard-smr-construction</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2885,6 +2936,7 @@
           <t>https://fedscoop.com/nist-chem-bio-ai-models/</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2936,6 +2988,7 @@
           <t>https://www.wam.ae/en/article/b5n9q21-abu-dhabi-gears-host-who-emergency-medical-teams</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2987,6 +3040,7 @@
           <t>https://www.bignewsnetwork.com/news/274695158/chemical-leak-triggers-emergency-in-texas</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3038,6 +3092,7 @@
           <t>https://bigislandnow.com/2024/10/11/2-new-monkeypox-cases-idd-in-hawaii/</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3089,6 +3144,7 @@
           <t>https://www.who.int/news/item/11-10-2024-second-round-of-polio-vaccination-in-the-gaza-strip-aims-to-vaccinate-over-half-a-million-children</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3140,6 +3196,7 @@
           <t>https://www.nucnet.org/news/gov-t-panel-rules-on-rehabilitation-of-ranger-uranium-mine-10-3-2024</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3191,6 +3248,7 @@
           <t>https://interestingengineering.com/Economic/us-firm-nuclear-fusion-device-prototype</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3242,6 +3300,7 @@
           <t>https://ukhsa.blog.gov.uk/2024/10/08/marburg-virus-disease-what-you-need-to-know/</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3293,6 +3352,7 @@
           <t>https://www.spectator.com.au/2024/10/australia-is-already-a-successful-nuclear-nation/</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3344,6 +3404,7 @@
           <t>https://www.msn.com/en-us/news/world/iranian-earthquake-sparks-debate-over-potential-nuclear-testing/ar-AA1sbEQI</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3395,6 +3456,7 @@
           <t>https://en.apa.az/social/azerbaijans-liberated-territories-has-nearly-1-million-167-thousand-hectares-of-hazardous-areas-anama-451169</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3446,6 +3508,7 @@
           <t>https://www.world-nuclear-news.org/articles/first-smr-projects-selected-by-european-industrial-alliance</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3497,6 +3560,7 @@
           <t>https://www.world-nuclear-news.org/articles/first-smr-projects-selected-by-european-industrial-alliance</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3548,6 +3612,7 @@
           <t>https://www.world-nuclear-news.org/articles/first-smr-projects-selected-by-european-industrial-alliance</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3599,6 +3664,7 @@
           <t>https://www.iranintl.com/en/202410142621</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3650,6 +3716,7 @@
           <t>https://www.nucnet.org/news/westinghouse-signs-nuclear-new-build-mou-with-shipbuilder-seaspan-10-1-2024</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3701,6 +3768,7 @@
           <t>https://www.jpost.com/breaking-news/article-824605</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3752,6 +3820,7 @@
           <t>https://en.sggp.org.vn/health-sector-strengthens-strict-quarantine-measures-to-prevent-marburg-disease-post113100.html</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3803,6 +3872,7 @@
           <t>https://www.iaea.org/newscenter/pressreleases/iaea-initiates-first-practical-steps-of-additional-measures-at-sea-near-fukushima-daiichi-nuclear-power-station</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3854,6 +3924,7 @@
           <t>https://www.ncr-iran.org/en/ncri-statements/statement-nuclear/khamenei-orders-acceleration-of-nuclear-weapon-production-to-ensure-iranian-regimes-survival/</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3905,6 +3976,7 @@
           <t>https://www.postandcourier.com/greenville/clemson-news/cdc-clemson-disease-software-flu-outbreaks/article_a6584d48-865d-11ef-a1e7-330ecfad26b5.html</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3956,6 +4028,7 @@
           <t>https://reliefweb.int/report/afghanistan/afghanistan-infectious-disease-outbreaks-epidemiological-week-40-29-sep-05-oct-2024-situation-report-40</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4007,6 +4080,7 @@
           <t>http://www.seychellesnewsagency.com/articles/21384/Seychelles+sets+up+new+chemical%2C+biological%2C+radiological+and+nuclear+team</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4058,6 +4132,7 @@
           <t>https://thewash.org/2024/10/15/columbia-heights-building-owners-fined-for-hazardous-unsafe-conditions-after-gas-explosion/</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4109,6 +4184,7 @@
           <t>https://www.world-nuclear-news.org/articles/brics-members-set-to-increase-nuclear-energy-cooperation</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4160,6 +4236,7 @@
           <t>https://www.world-nuclear-news.org/articles/brics-members-set-to-increase-nuclear-energy-cooperation</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4211,6 +4288,7 @@
           <t>https://www.army.mil/article/280511/seasoned_us_army_civilian_pilots_fly_missions_for_lifesaving_chemical_surety_program</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4262,6 +4340,7 @@
           <t>https://local21news.com/news/local/fire-crews-on-scene-of-hazardous-material-leak-at-water-treatment-plant-in-lebanon-county</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4313,6 +4392,7 @@
           <t>https://www.world-nuclear-news.org/articles/doe-signs-off-on-oklo-fuel-fabrication-facility-design</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4364,6 +4444,7 @@
           <t>https://www.nucnet.org/news/restarts-continue-with-shimane-2-due-back-online-in-december-10-3-2024</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4415,6 +4496,7 @@
           <t>https://www.scmp.com/tech/big-tech/article/3284168/chinese-state-owned-nuclear-company-claims-breakthrough-radiation-detection-chip</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4466,6 +4548,7 @@
           <t>https://www.timesofisrael.com/liveblog_entry/irans-atomic-agency-says-very-unlikely-israel-will-attack-nuclear-facilities/</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4517,6 +4600,7 @@
           <t>https://www.nucnet.org/news/adurenco-signs-enrichment-contract-with-french-htgr-developer-jimmy-10-5-2024</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4568,6 +4652,7 @@
           <t>https://www.world-nuclear-news.org/articles/amazon-invests-in-x-energy-unveils-smr-project-plans</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4619,6 +4704,7 @@
           <t>https://www.thesun.co.uk/news/31015676/oil-tanker-explosion-fire-germany/</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4670,6 +4756,7 @@
           <t>https://www.who.int/news/item/16-10-2024-parliamentarians-unite-in-berlin-to-sign-global-statement-supporting-the-who-pandemic-agreement</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4721,6 +4808,7 @@
           <t>https://www.aa.com.tr/en/europe/who-warns-risk-of-cholera-spread-very-high-in-lebanon/3364359</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4772,6 +4860,7 @@
           <t>https://menafn.com/1108780610/ADCMC-showcases-range-of-innovative-digital-initiatives-at-GITEX-Global-2024</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4823,6 +4912,7 @@
           <t>https://www.zawya.com/en/business/energy/fanr-board-reviews-regulatory-activities-at-barakah-approves-agreements-y6opk8sl</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4874,6 +4964,7 @@
           <t>https://www3.nhk.or.jp/nhkworld/en/news/20241016_02/</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4925,6 +5016,7 @@
           <t>https://www.wam.ae/en/article/b5q8w5z-uae-elected-chair-iaeas-steering-committee</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4976,6 +5068,7 @@
           <t>https://www.nucnet.org/news/doe-announces-usd900-million-funding-for-generation-iii-smr-deployment-10-4-2024</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5027,6 +5120,7 @@
           <t>https://www.nucnet.org/news/iaea-begins-additional-monitoring-measures-following-japan-and-china-agreement-10-5-2024</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5078,6 +5172,7 @@
           <t>https://www.nucnet.org/news/iaea-begins-additional-monitoring-measures-following-japan-and-china-agreement-10-5-2024</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5129,6 +5224,7 @@
           <t>https://www.iaea.org/newscenter/pressreleases/update-255-iaea-director-general-statement-on-situation-in-ukraine</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5180,6 +5276,7 @@
           <t>https://www.bta.bg/en/news/economy/763988-two-sheep-farms-with-smallpox-infection-identified-in-southern-bulgaria-in-two-d</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5231,6 +5328,7 @@
           <t>https://dailynewshungary.com/bird-flu-detected-at-more-farms-in-hungary/</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5282,6 +5380,7 @@
           <t>https://www.world-nuclear-news.org/articles/japanese-data-centre-seeks-nuclear-electricity-supplies</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5333,6 +5432,7 @@
           <t>https://www.who.int/news/item/17-10-2024-who-in-lebanon-working-to-stop-cholera-spread-amid-conflict</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5384,6 +5484,7 @@
           <t>https://www.world-nuclear-news.org/articles/framatome-to-supply-hungarian-plant-with-nuclear-fuel</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5435,6 +5536,7 @@
           <t>https://www.iaea.org/newscenter/pressreleases/iaea-mission-recognizes-latvias-commitment-to-improve-nuclear-and-radiation-safety-encourages-continued-improvements</t>
         </is>
       </c>
+      <c r="L98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5486,6 +5588,7 @@
           <t>https://www.iaea.org/newscenter/pressreleases/tritium-level-far-below-japans-operational-limit-in-tenth-batch-of-alps-treated-water-iaea-confirms</t>
         </is>
       </c>
+      <c r="L99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5537,6 +5640,7 @@
           <t>https://www.iaea.org/newscenter/news/setting-the-agenda-regional-cooperative-agreement-representatives-convene-at-iaea-general-conference-to-review-activities-establish-priorities</t>
         </is>
       </c>
+      <c r="L100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5588,6 +5692,7 @@
           <t>https://www.fdd.org/analysis/2024/10/08/possible-targets-in-iran-Economic-nuclear-and-regime-infrastructure/</t>
         </is>
       </c>
+      <c r="L101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5639,6 +5744,7 @@
           <t>https://www.iaea.org/newscenter/news/international-conference-on-small-modular-reactors-next-week</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5690,6 +5796,7 @@
           <t>https://business.inquirer.net/485687/japan-shifting-back-to-nuclear-to-ditch-coal-power-ai</t>
         </is>
       </c>
+      <c r="L103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5741,6 +5848,7 @@
           <t>https://www.al.com/news/2024/10/fire-breaks-out-at-oxfords-tull-chemical-company.html</t>
         </is>
       </c>
+      <c r="L104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5792,6 +5900,7 @@
           <t>https://www.who.int/macaochina/news/detail-wpro/24-10-2024-regional-health-leaders-agree-to-improve-financing-to-achieve-universal-health-coverage--prioritize-digital-health</t>
         </is>
       </c>
+      <c r="L105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5843,6 +5952,7 @@
           <t>https://www.fananews.com/language/en/morocco-hosts-international-conference-on-ai-chemical-weapons-convention-in-partnership-with-organisation-for-prohibition-of-chemical-weapons/</t>
         </is>
       </c>
+      <c r="L106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5894,6 +6004,7 @@
           <t>https://menafn.com/arabic/1108798677/%D8%A7%D9%84%D8%A7%D9%94%D8%B1%D8%AF%D9%86-%D9%85%D9%88%D9%94%D9%87%D9%84-%D9%84%D9%84%D8%AD%D8%B5%D9%88%D9%84-%D8%B9%D9%84%D9%89-%D8%AA%D9%85%D9%88%D9%8A%D9%84-%D9%84%D8%A7%D9%95%D8%AF%D8%A7%D8%B1%D8%A9-%D8%A7%D9%84%D9%85%D9%88%D8%A7%D8%AF-%D8%A7%D9%84%D9%83%D9%8A%D9%85%D9%8A%D8%A7%D9%8A%D9%94%D9%8A%D8%A9-%D9%88%D8%A7%D9%84%D9%86%D9%81%D8%A7%D9%8A%D8%A7%D8%AA</t>
         </is>
       </c>
+      <c r="L107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5945,6 +6056,7 @@
           <t>https://www.standardmedia.co.ke/health/counties/article/2001439117/uganda-delegation-commends-kenyas-radiation-safety</t>
         </is>
       </c>
+      <c r="L108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5996,6 +6108,7 @@
           <t>https://www.afro.who.int/countries/south-sudan/news/severe-flooding-compounds-health-crisis-south-sudan</t>
         </is>
       </c>
+      <c r="L109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6047,6 +6160,7 @@
           <t>https://www.who.int/news/item/21-10-2024-viet-nam-eliminates-trachoma-as-a-public-health-problem</t>
         </is>
       </c>
+      <c r="L110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6098,6 +6212,7 @@
           <t>https://newhampshirebulletin.com/2024/10/21/the-mosquito-borne-virus-triple-e-continues-its-spread-worrying-state-health-officials/</t>
         </is>
       </c>
+      <c r="L111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6149,6 +6264,7 @@
           <t>https://www.iaea.org/newscenter/news/the-state-of-eritrea-signs-its-third-country-programme-framework-cpf-for-2024-2028</t>
         </is>
       </c>
+      <c r="L112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6200,6 +6316,7 @@
           <t>https://www.world-nuclear-news.org/articles/serbia-continues-discussions-on-future-nuclear-projects</t>
         </is>
       </c>
+      <c r="L113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6251,6 +6368,7 @@
           <t>https://www.tehrantimes.com/news/505287/Iran-may-reassess-nuclear-policies-if-sites-are-attacked-source</t>
         </is>
       </c>
+      <c r="L114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6302,6 +6420,7 @@
           <t>https://www.sustainableviews.com/ombudsman-condemns-european-commission-for-failing-to-control-hazardous-chemicals-44927379/</t>
         </is>
       </c>
+      <c r="L115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6353,6 +6472,7 @@
           <t>https://www.sustainableviews.com/ombudsman-condemns-european-commission-for-failing-to-control-hazardous-chemicals-44927379/</t>
         </is>
       </c>
+      <c r="L116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6404,6 +6524,7 @@
           <t>https://www.sustainableviews.com/ombudsman-condemns-european-commission-for-failing-to-control-hazardous-chemicals-44927379/</t>
         </is>
       </c>
+      <c r="L117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6455,6 +6576,7 @@
           <t>https://www.zawya.com/en/business/healthcare/killer-diseases-put-focus-on-kenyas-health-care-iqx0b5qc</t>
         </is>
       </c>
+      <c r="L118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6506,6 +6628,7 @@
           <t>https://www.enerdata.net/publications/daily-energy-news/china-issues-operation-licence-unit-1-zhangzhou-nuclear-plant.html</t>
         </is>
       </c>
+      <c r="L119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6557,6 +6680,7 @@
           <t>https://gulfnews.com/business/markets/investments-of-13b-in-saudi-arabias-healthcare-sector-unveil-during-global-health-exhibition-in-riyadh-1.1729589734070</t>
         </is>
       </c>
+      <c r="L120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6608,6 +6732,7 @@
           <t>https://www.fox13seattle.com/news/bird-flu-wa</t>
         </is>
       </c>
+      <c r="L121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6659,6 +6784,7 @@
           <t>https://telegrafi.com/en/hazardous-waste-containers-arrive-in-Durres-on-Sunday/</t>
         </is>
       </c>
+      <c r="L122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6710,6 +6836,7 @@
           <t>https://asianews.network/who-confirms-vietnam-has-eliminated-trachoma/</t>
         </is>
       </c>
+      <c r="L123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6761,6 +6888,7 @@
           <t>https://healthcareasiamagazine.com/healthcare/news/uae-increases-health-funding-amidst-economic-diversification-effort</t>
         </is>
       </c>
+      <c r="L124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6812,6 +6940,7 @@
           <t>https://www.health.govt.nz/publications/ministry-of-health-annual-report-for-the-year-ended-30-june-2024</t>
         </is>
       </c>
+      <c r="L125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6863,6 +6992,7 @@
           <t>https://www.zawya.com/en/press-release/events-and-conferences/abhi-uk-pavilion-highlights-transformative-healthtech-innovations-at-global-health-exhibition-in-saudi-arabia-b8l3ocfl</t>
         </is>
       </c>
+      <c r="L126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6914,6 +7044,7 @@
           <t>https://mediaoffice.ae/en/news/2024/october/21-10/healthcare-future-summit-2024</t>
         </is>
       </c>
+      <c r="L127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6965,6 +7096,7 @@
           <t>https://www.euronews.com/health/2024/10/22/leaked-budget-plans-spark-fears-for-eu-health-budget</t>
         </is>
       </c>
+      <c r="L128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7016,6 +7148,7 @@
           <t>https://www.euronews.com/health/2024/10/22/leaked-budget-plans-spark-fears-for-eu-health-budget</t>
         </is>
       </c>
+      <c r="L129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7067,6 +7200,7 @@
           <t>https://www.euronews.com/health/2024/10/22/leaked-budget-plans-spark-fears-for-eu-health-budget</t>
         </is>
       </c>
+      <c r="L130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7118,6 +7252,7 @@
           <t>https://www.app.com.pk/domestic/dengue-cases-surge-with-97-new-infections-reported/</t>
         </is>
       </c>
+      <c r="L131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7169,6 +7304,7 @@
           <t>https://www.theguardian.com/environment/2024/oct/21/uk-rivers-chemicals-stimulants-phosphates-nintrate-endangering-aquatic-life</t>
         </is>
       </c>
+      <c r="L132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7220,6 +7356,7 @@
           <t>https://www.thenews.com.pk/latest/1242702-air-quality-in-lahore-drops-to-hazardous</t>
         </is>
       </c>
+      <c r="L133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7271,6 +7408,7 @@
           <t>https://www.powderbulksolids.com/industrial-fires-explosions/federal-lawsuit-filed-against-biolab-for-chemical-release-fire</t>
         </is>
       </c>
+      <c r="L134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7322,6 +7460,7 @@
           <t>https://www.opcw.org/media-centre/news/2024/10/2024-opcw-associate-programme-concludes-hague</t>
         </is>
       </c>
+      <c r="L135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7373,6 +7512,7 @@
           <t>https://al24news.com/en/iran-warns-iaea-about-zionist-entity-threats-to-nuclear-sites/</t>
         </is>
       </c>
+      <c r="L136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7424,6 +7564,7 @@
           <t>https://regtechtimes.com/north-korea-gets-nuclear-help-from-russia-in-exch/</t>
         </is>
       </c>
+      <c r="L137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7475,6 +7616,7 @@
           <t>https://healthcareasiamagazine.com/healthcare/news/abu-dhabis-doh-unveils-sahatna-platform-proactive-health-mgmt</t>
         </is>
       </c>
+      <c r="L138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7526,6 +7668,7 @@
           <t>https://www.bna.bh/en/HealthMinisterdiscusseshealthcooperationwithEgyptiancounterpart.aspx?cms=q8FmFJgiscL2fwIzON1%2BDgvZcgSkeUomlF7ra61uAvQ%3D</t>
         </is>
       </c>
+      <c r="L139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7577,6 +7720,7 @@
           <t>https://economictimes.indiatimes.com/news/international/world-news/tried-to-kill-nuclear-scientist-israel-arrests-7-jerusalem-residents-allegedly-plotting-attacks-for-iran/videoshow/114474179.cms?from=mdr</t>
         </is>
       </c>
+      <c r="L140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7628,6 +7772,7 @@
           <t>https://www.wlbt.com/2024/10/23/mississippi-public-service-commission-hosts-summit-future-nuclear-power-state/</t>
         </is>
       </c>
+      <c r="L141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7679,6 +7824,7 @@
           <t>https://www.bna.bh/en/HealthMinisterparticipatesinPHDCGlobalConference.aspx?cms=q8FmFJgiscL2fwIzON1%2BDnw8CXsPMB0KW78z%2FqJE8w8%3D</t>
         </is>
       </c>
+      <c r="L142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7730,6 +7876,7 @@
           <t>https://english.alarabiya.net/News/world/2024/10/23/putin-erdogan-to-discuss-nuclear-power-plants-gas-hub-on-sidelines-of-brics-</t>
         </is>
       </c>
+      <c r="L143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7781,6 +7928,7 @@
           <t>https://www.world-nuclear-news.org/articles/reactor-assembly-completed-for-bangladeshs-first-nuclear-plant</t>
         </is>
       </c>
+      <c r="L144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7832,6 +7980,7 @@
           <t>https://www.thehindu.com/news/national/indias-fourth-nuclear-submarine-launched-into-water/article68783731.ece</t>
         </is>
       </c>
+      <c r="L145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7883,6 +8032,7 @@
           <t>https://www.neimagazine.com/news/latvia-improves-nuclear-safety-infrastructure/</t>
         </is>
       </c>
+      <c r="L146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7934,6 +8084,7 @@
           <t>https://www.gulf-times.com/article/693061/qatar/qatar-reaffirms-commitment-to-continuing-efforts-toward-elimination-of-nuclear-weapons-and-nuclear-non-proliferation</t>
         </is>
       </c>
+      <c r="L147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7985,6 +8136,7 @@
           <t>https://maritime-executive.com/article/nuclear-transport-ship-to-test-uk-s-first-rigid-sail</t>
         </is>
       </c>
+      <c r="L148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8036,6 +8188,7 @@
           <t>https://web.uniroma2.it/it/contenuto/eventi-cbrne-aspetti-organizzativi-e-clinici-il-convegno-per-la-formazione</t>
         </is>
       </c>
+      <c r="L149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8087,6 +8240,7 @@
           <t>https://www.aa.com.tr/en/energy/nuclear/iran-submits-protest-note-to-iaea-over-israeli-threats-to-nuclear-sites/44088?amp=1</t>
         </is>
       </c>
+      <c r="L150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8138,6 +8292,7 @@
           <t>https://www.zawya.com/en/business/healthcare/sdaia-and-health-ministry-agree-to-cooperate-in-managing-national-data-in-saudi-health-sector-p7a9n4fv</t>
         </is>
       </c>
+      <c r="L151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8189,6 +8344,7 @@
           <t>https://en.trend.az/business/3960432.html</t>
         </is>
       </c>
+      <c r="L152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8240,6 +8396,7 @@
           <t>https://www.iaea.org/newscenter/news/iaea-initiative-to-streamline-smr-deployment-moving-to-implementation-phase</t>
         </is>
       </c>
+      <c r="L153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8291,6 +8448,7 @@
           <t>https://www.mediaoffice.abudhabi/en/health/purehealth-launches-technology-platform-to-enhance-access-to-remote-healthcare-services/</t>
         </is>
       </c>
+      <c r="L154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8342,6 +8500,7 @@
           <t>https://www.neimagazine.com/news/vietnam-proposes-sole-state-investment-in-nuclear/</t>
         </is>
       </c>
+      <c r="L155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8393,6 +8552,7 @@
           <t>https://www.thestar.com/politics/provincial/ford-government-says-ontario-needs-more-nuclear-power-to-tackle-rising-demand/article_5549a7b4-9169-11ef-8c0f-073525b0bd93.html</t>
         </is>
       </c>
+      <c r="L156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8444,6 +8604,7 @@
           <t>https://www.neimagazine.com/news/iaea-reports-ongoing-threats-at-zaporizhia/</t>
         </is>
       </c>
+      <c r="L157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8495,6 +8656,7 @@
           <t>https://www.observer24.com.na/nuclear-science-and-technology-conference-aims-to-unlock-development-potential/</t>
         </is>
       </c>
+      <c r="L158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8546,6 +8708,7 @@
           <t>https://foreignpolicy.com/2024/10/24/iran-nuclear-israel-strategy-weapons-missiles-hamas-hezbollah-axis-resistance/</t>
         </is>
       </c>
+      <c r="L159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8597,6 +8760,7 @@
           <t>https://www.bworldonline.com/the-nation/2024/10/23/630309/manila-bats-for-cooperation-in-global-nuclear-testing-monitoring-system/</t>
         </is>
       </c>
+      <c r="L160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8648,6 +8812,7 @@
           <t>https://www.miragenews.com/nuclear-energy-hearing-program-launches-in-1343078/</t>
         </is>
       </c>
+      <c r="L161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8699,6 +8864,7 @@
           <t>https://jamaica-gleaner.com/article/news/20241024/jamaica-signs-mou-canadian-firms-nuclear-energy</t>
         </is>
       </c>
+      <c r="L162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8750,6 +8916,7 @@
           <t>https://today.ucsd.edu/story/innovative-bioelectronic-device-offers-new-hope-in-the-fight-against-bacterial-infections</t>
         </is>
       </c>
+      <c r="L163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8801,6 +8968,7 @@
           <t>https://www.thehealthsite.com/news/bird-flu-outbreak-in-us-total-tally-of-human-infections-rises-to-31-in-the-country-1142080/</t>
         </is>
       </c>
+      <c r="L164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8852,6 +9020,7 @@
           <t>https://www.iaea.org/newscenter/pressreleases/iaea-completes-international-physical-protection-advisory-service-mission-in-the-republic-of-the-congo</t>
         </is>
       </c>
+      <c r="L165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8904,6 +9073,7 @@
           <t>https://www.nbcnews.com/news/amp-video/mmvo222743109617</t>
         </is>
       </c>
+      <c r="L166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8955,6 +9125,7 @@
           <t>https://www.timesofisrael.com/liveblog_entry/at-least-5-explosions-reportedly-heard-near-tehran/</t>
         </is>
       </c>
+      <c r="L167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -9006,6 +9177,7 @@
           <t>https://www.iaea.org/newscenter/pressreleases/update-256-iaea-director-general-statement-on-situation-in-ukraine</t>
         </is>
       </c>
+      <c r="L168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -9057,6 +9229,7 @@
           <t>https://www.arabnews.pk/node/2576517/pakistan</t>
         </is>
       </c>
+      <c r="L169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9108,6 +9281,7 @@
           <t>https://www.globalconstructionreview.com/russia-promotes-nuclear-plant-for-proposed-new-mongolian-city/</t>
         </is>
       </c>
+      <c r="L170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9159,6 +9333,7 @@
           <t>https://www.globalconstructionreview.com/russia-promotes-nuclear-plant-for-proposed-new-mongolian-city/</t>
         </is>
       </c>
+      <c r="L171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -9210,6 +9385,7 @@
           <t>https://www.myjoyonline.com/rwanda-says-no-community-transmission-of-marburg-virus-with-zero-new-infections-in-recent-days/</t>
         </is>
       </c>
+      <c r="L172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -9261,6 +9437,7 @@
           <t>https://www.dvidshub.net/video/941147/b-roll-package-sky-soldiers-conduct-cbrn-training-during-e3b</t>
         </is>
       </c>
+      <c r="L173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -9312,6 +9489,7 @@
           <t>https://www.meed.com/uae-to-take-nuclear-plant-next-step</t>
         </is>
       </c>
+      <c r="L174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -9363,6 +9541,7 @@
           <t>https://www.world-nuclear-news.org/articles/mochovce-4-passes-safety-system-tests</t>
         </is>
       </c>
+      <c r="L175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -9414,6 +9593,7 @@
           <t>https://bukvy.org/en/250-cases-of-russia-using-chemical-weapons-in-ukraine-recorded-in-september/</t>
         </is>
       </c>
+      <c r="L176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9465,6 +9645,7 @@
           <t>https://bukvy.org/en/250-cases-of-russia-using-chemical-weapons-in-ukraine-recorded-in-september/</t>
         </is>
       </c>
+      <c r="L177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -9516,6 +9697,7 @@
           <t>https://www.defensenews.com/pentagon/2024/10/24/china-leading-rapid-expansion-of-nuclear-arsenal-pentagon-says/</t>
         </is>
       </c>
+      <c r="L178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -9567,6 +9749,7 @@
           <t>https://en.trend.az/business/3961814.html</t>
         </is>
       </c>
+      <c r="L179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -9618,6 +9801,7 @@
           <t>https://energycapitalpower.com/senegal-to-establish-nuclear-reactors-for-training-research/</t>
         </is>
       </c>
+      <c r="L180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9669,6 +9853,7 @@
           <t>https://www.wam.ae/en/article/b5uex8n-ajman-chamber-participates-16th-arab-german-health</t>
         </is>
       </c>
+      <c r="L181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9720,6 +9905,7 @@
           <t>https://www.neimagazine.com/news/slovenia-calls-off-nuclear-referendum/</t>
         </is>
       </c>
+      <c r="L182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9771,6 +9957,7 @@
           <t>https://www.wam.ae/en/article/b5uexhe-doh-accenture-collaborate-drive-digital</t>
         </is>
       </c>
+      <c r="L183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -9822,6 +10009,7 @@
           <t>https://www.travelandtourworld.com/news/article/singapore-thailand-implement-health-screenings-amid-rise-in-mpox-infections/</t>
         </is>
       </c>
+      <c r="L184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -9873,6 +10061,7 @@
           <t>https://www.travelandtourworld.com/news/article/singapore-thailand-implement-health-screenings-amid-rise-in-mpox-infections/</t>
         </is>
       </c>
+      <c r="L185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9924,6 +10113,7 @@
           <t>https://www.ucanews.com/news/japan-renews-focus-on-nuclear-energy-post-fukushima/106776</t>
         </is>
       </c>
+      <c r="L186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9975,6 +10165,7 @@
           <t>https://executivegov.com/2024/10/dia-nuclear-threat-report-china-russia-iran-north-korea/</t>
         </is>
       </c>
+      <c r="L187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -10026,6 +10217,7 @@
           <t>https://bulawayo24.com/index-id-news-sc-national-byo-246963.html</t>
         </is>
       </c>
+      <c r="L188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -10077,6 +10269,7 @@
           <t>https://www.romania-insider.com/contract-new-nuclear-reactors-romania-october-2024</t>
         </is>
       </c>
+      <c r="L189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -10128,6 +10321,7 @@
           <t>https://www.japantimes.co.jp/news/2024/10/28/japan/tepco-debris-removal-trial/</t>
         </is>
       </c>
+      <c r="L190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -10179,6 +10373,7 @@
           <t>https://www.euronews.com/2024/10/16/spanish-police-intercept-13-tonnes-of-chemical-weapons-precursors-bound-for-russia</t>
         </is>
       </c>
+      <c r="L191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -10230,6 +10425,7 @@
           <t>https://www.newsweek.com/russia-ukraine-drones-oil-fire-1968024</t>
         </is>
       </c>
+      <c r="L192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -10281,6 +10477,7 @@
           <t>https://www.marineinsight.com/shipping-news/russian-ship-to-unload-20000-tons-of-dangerous-cargo-at-great-yarmouth-port/</t>
         </is>
       </c>
+      <c r="L193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -10332,6 +10529,7 @@
           <t>https://english.alarabiya.net/News/world/2024/10/29/putin-orders-strategic-nuclear-training-exercise</t>
         </is>
       </c>
+      <c r="L194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -10383,6 +10581,7 @@
           <t>https://www.wkyufm.org/news/2024-10-29/meet-americas-secret-team-of-nuclear-first-responders</t>
         </is>
       </c>
+      <c r="L195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -10434,6 +10633,7 @@
           <t>https://www.reuters.com/world/africa/zimbabwe-reports-first-two-mpox-cases-unspecified-variant-2024-10-13/</t>
         </is>
       </c>
+      <c r="L196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -10485,6 +10685,7 @@
           <t>https://www3.nhk.or.jp/nhkworld/en/news/20241029_26/</t>
         </is>
       </c>
+      <c r="L197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -10536,6 +10737,7 @@
           <t>https://saintjohn.ca/en/news-and-notices/full-scale-nuclear-emergency-exercise-set-october-29-and-30</t>
         </is>
       </c>
+      <c r="L198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -10587,6 +10789,7 @@
           <t>https://www.wxow.com/news/van-orden-attends-nuclear-energy-roundtable/article_031ee7f8-9572-11ef-a320-03dcf6932c77.html</t>
         </is>
       </c>
+      <c r="L199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -10638,6 +10841,7 @@
           <t>https://www.iaea.org/newscenter/pressreleases/independent-review-assesses-iaeas-internal-safety-regulatory-system-for-first-time-finds-well-established-framework</t>
         </is>
       </c>
+      <c r="L200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -10689,6 +10893,7 @@
           <t>https://www.allsides.com/news/2024-10-09-1415/coronavirus-covid-may-increase-risk-death-years-after-infection-study</t>
         </is>
       </c>
+      <c r="L201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -10740,6 +10945,7 @@
           <t>https://ctif.org/events/7th-international-conference-cbrne-research-and-innovation-2026</t>
         </is>
       </c>
+      <c r="L202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -10791,6 +10997,7 @@
           <t>https://www.nucnet.org/news/voters-back-nuclear-power-plant-construction-in-national-referendum-10-1-2024</t>
         </is>
       </c>
+      <c r="L203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -10842,6 +11049,7 @@
           <t>https://www.nucnet.org/news/industry-lays-groundwork-for-reactor-deployment-with-first-comprehensive-set-of-rules-10-1-2024</t>
         </is>
       </c>
+      <c r="L204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -10893,6 +11101,7 @@
           <t>https://www.nucnet.org/news/nucnet-launches-global-small-modular-and-advanced-reactor-database-10-4-2024</t>
         </is>
       </c>
+      <c r="L205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -10944,6 +11153,7 @@
           <t>https://interestingengineering.com/Economic/plasma-heating-prediction-made-10-million-times-faster</t>
         </is>
       </c>
+      <c r="L206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -10995,6 +11205,7 @@
           <t>https://www.iaea.org/newscenter/news/from-preparedness-to-resilience-the-role-of-the-iaea-in-nuclear-and-radiological-emergency-response</t>
         </is>
       </c>
+      <c r="L207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -11046,6 +11257,7 @@
           <t>https://scitechdaily.com/revolutionizing-virology-ai-discovers-over-160000-new-rna-viruses/</t>
         </is>
       </c>
+      <c r="L208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -11097,6 +11309,7 @@
           <t>https://redirect.viglink.com?u=https%3A%2F%2Fwww.nature.com%2Farticles%2Fs41467-024-53085-9&amp;key=a7e37b5f6ff1de9cb410158b1013e54a&amp;prodOvrd=RAC&amp;opt=false</t>
         </is>
       </c>
+      <c r="L209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -11148,6 +11361,7 @@
           <t>https://interestingengineering.com/Economic/uranium-enrichment-urenco-centrifuge-milestones</t>
         </is>
       </c>
+      <c r="L210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -11199,6 +11413,7 @@
           <t>https://www.wam.ae/en/article/b5ogl9j-new-risks-raise-pandemic-threat-global-scale-who</t>
         </is>
       </c>
+      <c r="L211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -11250,6 +11465,7 @@
           <t>https://www.nucnet.org/news/google-signs-world-first-deal-to-buy-power-from-small-modular-reactors-for-data-centres-10-2-2024</t>
         </is>
       </c>
+      <c r="L212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -11301,6 +11517,7 @@
           <t>https://www.iaea.org/newscenter/news/2023-iaea-annual-report-presented-to-the-un-general-assembly</t>
         </is>
       </c>
+      <c r="L213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -11352,6 +11569,7 @@
           <t>https://www.who.int/publications/i/item/9789240101456</t>
         </is>
       </c>
+      <c r="L214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -11403,6 +11621,7 @@
           <t>https://www.nucnet.org/news/agency-plans-next-workshops-in-bid-to-advance-nuclear-inn-europe-and-eurasia-10-4-2024</t>
         </is>
       </c>
+      <c r="L215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -11454,6 +11673,7 @@
           <t>https://www.nucnet.org/news/alliance-calls-for-commission-to-fully-recognise-nuclear-in-paradigm-policy-shift-10-4-2024</t>
         </is>
       </c>
+      <c r="L216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -11505,6 +11725,7 @@
           <t>https://www.who.int/publications/i/item/9789240098619</t>
         </is>
       </c>
+      <c r="L217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -11533,7 +11754,7 @@
         </is>
       </c>
       <c r="F218" s="2" t="n">
-        <v>2024</v>
+        <v>45489</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -11556,6 +11777,7 @@
           <t>https://www.iaea.org/publications/15790/small-modular-reactors-advances-in-smr-developments-2024</t>
         </is>
       </c>
+      <c r="L218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -11607,6 +11829,7 @@
           <t>https://www.iaea.org/newscenter/news/new-coordinated-research-project-crp-optimizing-mining-wastewater-remediation</t>
         </is>
       </c>
+      <c r="L219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -11658,6 +11881,7 @@
           <t>https://www.nucnet.org/news/investment-in-nuclear-must-rapidly-increase-to-usd125-billion-a-year-10-1-2024</t>
         </is>
       </c>
+      <c r="L220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -11709,6 +11933,7 @@
           <t>https://www.catf.us/resource/global-race-advanced-nuclear/</t>
         </is>
       </c>
+      <c r="L221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -11760,6 +11985,7 @@
           <t>https://www.dia.mil/News-Features/Articles/Article-View/Article/3943315/dia-releases-nuclear-challenges-intelligence-overview/</t>
         </is>
       </c>
+      <c r="L222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -11811,6 +12037,7 @@
           <t>https://www.hazardexonthenet.net/article/210054/COBIC-Ex-unveils-F112-LT-Ex--Explosion-proof-laptop-for-hazardous-environments.aspx</t>
         </is>
       </c>
+      <c r="L223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -11862,6 +12089,7 @@
           <t>https://www.barrons.com/articles/google-amazon-ai-nuclear-waste-16fb39ab</t>
         </is>
       </c>
+      <c r="L224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -11913,6 +12141,7 @@
           <t>https://www.iaea.org/publications/15295/modelling-the-contribution-of-nuclear-energy-to-economic-development</t>
         </is>
       </c>
+      <c r="L225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -11964,6 +12193,7 @@
           <t>https://www.unep.org/news-and-stories/speech/global-action-plan-health-through-biodiversity</t>
         </is>
       </c>
+      <c r="L226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -12015,6 +12245,7 @@
           <t>https://www.who.int/news-room/events/detail/2024/10/30/default-calendar/g20-high-level-meeting-on-one-health</t>
         </is>
       </c>
+      <c r="L227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -12066,6 +12297,7 @@
           <t>https://www.who.int/news/item/29-10-2024-who-and-partners-activate-global-health-emergency-corps-for-the-first-time-in-response-to-mpox-outbreak</t>
         </is>
       </c>
+      <c r="L228" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
